--- a/Data/Hires/Workday_NewHire_UKNI_Regression_PK14.xlsx
+++ b/Data/Hires/Workday_NewHire_UKNI_Regression_PK14.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39149D1C-43F5-45DB-BD56-C2BA42253A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C570752-E392-40F3-91AD-21811B6FBEBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="224">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -213,7 +213,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10697621</t>
+    <t>10697719</t>
   </si>
   <si>
     <t>Passed</t>
@@ -231,7 +231,7 @@
     <t>UkOne</t>
   </si>
   <si>
-    <t>TwentyFiveMarchTwentyFive</t>
+    <t>TwentyFiveAprilSeven</t>
   </si>
   <si>
     <t>161 923 4772</t>
@@ -312,7 +312,7 @@
     <t>National Insurance (NI) Number</t>
   </si>
   <si>
-    <t>AB911805A</t>
+    <t>AB911835A</t>
   </si>
   <si>
     <t>Male</t>
@@ -345,7 +345,7 @@
     <t>Test2</t>
   </si>
   <si>
-    <t>10697622</t>
+    <t>Failed</t>
   </si>
   <si>
     <t>519 Store Management (Zerab Sepupu (9575064))</t>
@@ -354,7 +354,7 @@
     <t>UkTwo</t>
   </si>
   <si>
-    <t>Auto 78586154</t>
+    <t>Auto 85284722</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -366,7 +366,7 @@
     <t xml:space="preserve">251 Management Retail </t>
   </si>
   <si>
-    <t>AB911806A</t>
+    <t>AB911836A</t>
   </si>
   <si>
     <t>UK Management Group 60</t>
@@ -375,22 +375,19 @@
     <t>Test3</t>
   </si>
   <si>
-    <t>Test failed for 'UkThree TwentyFiveMarchTwentyFive' Employee: Errors and AlertsErrorPage Error- You have not entered an amount within the Compensation Guidelines.     (Employee Compensation Event For Hire Employee) &amp; find failed Screenshot Path:-&gt;H:\WorkdayPlaywright/WorkdayFailedScreenshot/2025-03-25T01-33-02-460Z.png</t>
-  </si>
-  <si>
-    <t>Failed</t>
+    <t>Test failed for 'UkThree TwentyFiveAprilSeven' Employee: Errors and AlertsErrorPage Error- You have not entered an amount within the Compensation Guidelines.     (Employee Compensation Event For Hire Employee) &amp; find failed Screenshot Path:-&gt;H:\WorkdayPlaywright/WorkdayFailedScreenshot/2025-04-08T05-49-09-003Z.png</t>
   </si>
   <si>
     <t>UkThree</t>
   </si>
   <si>
-    <t>Auto 87338179</t>
+    <t>Auto 47476690</t>
   </si>
   <si>
     <t>Assistant Manager</t>
   </si>
   <si>
-    <t>AB911807A</t>
+    <t>AB911837A</t>
   </si>
   <si>
     <t>Passed after removing Grade Profile and Step</t>
@@ -402,7 +399,7 @@
     <t>UkFour</t>
   </si>
   <si>
-    <t>Auto 74109205</t>
+    <t>Auto 37859426</t>
   </si>
   <si>
     <t>Fixed Term (Fixed Term)</t>
@@ -414,7 +411,7 @@
     <t>50000</t>
   </si>
   <si>
-    <t>AB911808A</t>
+    <t>AB911838A</t>
   </si>
   <si>
     <t>UK Department Manager 1</t>
@@ -426,10 +423,13 @@
     <t>Test5</t>
   </si>
   <si>
+    <t>10697763</t>
+  </si>
+  <si>
     <t>UkFive</t>
   </si>
   <si>
-    <t>Auto 5201488</t>
+    <t>Auto 82620489</t>
   </si>
   <si>
     <t>Team Manager - Retail</t>
@@ -438,7 +438,7 @@
     <t>Part time</t>
   </si>
   <si>
-    <t>AB911809A</t>
+    <t>AB911839A</t>
   </si>
   <si>
     <t>Retail - Team Manager</t>
@@ -450,19 +450,19 @@
     <t>Test6</t>
   </si>
   <si>
-    <t>10697625</t>
+    <t>10697722</t>
   </si>
   <si>
     <t>UkSix</t>
   </si>
   <si>
-    <t>Auto 18412848</t>
+    <t>Auto 42362593</t>
   </si>
   <si>
     <t>Visual Merchandising Manager</t>
   </si>
   <si>
-    <t>AB911810A</t>
+    <t>AB911840A</t>
   </si>
   <si>
     <t>UK Visual Merchandising Manager 1</t>
@@ -474,16 +474,19 @@
     <t>Test7</t>
   </si>
   <si>
+    <t>10697764</t>
+  </si>
+  <si>
     <t>UkSeven</t>
   </si>
   <si>
-    <t>Auto 79583787</t>
+    <t>Auto 69844681</t>
   </si>
   <si>
     <t>P&amp;C Manager Stores</t>
   </si>
   <si>
-    <t>AB911811A</t>
+    <t>AB911841A</t>
   </si>
   <si>
     <t>UK Assistant Manager</t>
@@ -495,27 +498,27 @@
     <t>Test8</t>
   </si>
   <si>
+    <t>10697723</t>
+  </si>
+  <si>
     <t>UkEight</t>
   </si>
   <si>
     <t>261 Tills</t>
   </si>
   <si>
-    <t>AB911812A</t>
+    <t>AB911842A</t>
   </si>
   <si>
     <t>Test9</t>
   </si>
   <si>
-    <t>10697634</t>
+    <t>10697724</t>
   </si>
   <si>
     <t>UkNine</t>
   </si>
   <si>
-    <t>TwentyFiveMarchTwentyFiveA</t>
-  </si>
-  <si>
     <t>Visual Merchandiser</t>
   </si>
   <si>
@@ -528,12 +531,15 @@
     <t>Initial Step-GB VM Nat -23+</t>
   </si>
   <si>
-    <t>AB711813A</t>
+    <t>AB911843A</t>
   </si>
   <si>
     <t>Test10</t>
   </si>
   <si>
+    <t>10697725</t>
+  </si>
+  <si>
     <t>UkTen</t>
   </si>
   <si>
@@ -543,40 +549,43 @@
     <t>250 Human Resources Retail</t>
   </si>
   <si>
-    <t>AB911814A</t>
+    <t>AB911844A</t>
   </si>
   <si>
     <t>Test11</t>
   </si>
   <si>
-    <t>Test failed for 'UkEleven TwentyFiveMarchTwentyFive' Employee: Errors and AlertsErrorPage Error- You have not entered an amount within the Compensation Guidelines.     (Employee Compensation Event For Hire Employee) &amp; find failed Screenshot Path:-&gt;H:\WorkdayPlaywright/WorkdayFailedScreenshot/2025-03-25T02-23-47-911Z.png</t>
+    <t>Test failed for 'UkEleven TwentyFiveAprilSeven' Employee: Errors and AlertsErrorPage Error- You have not entered an amount within the Compensation Guidelines.     (Employee Compensation Event For Hire Employee) &amp; find failed Screenshot Path:-&gt;H:\WorkdayPlaywright/WorkdayFailedScreenshot/2025-04-08T05-15-08-030Z.png</t>
   </si>
   <si>
     <t>UkEleven</t>
   </si>
   <si>
-    <t>Auto 10257924</t>
-  </si>
-  <si>
-    <t>AB911815A</t>
+    <t>Auto 80749403</t>
+  </si>
+  <si>
+    <t>AB911845A</t>
   </si>
   <si>
     <t>Test12</t>
   </si>
   <si>
+    <t>10697726</t>
+  </si>
+  <si>
     <t>UkTwelve</t>
   </si>
   <si>
-    <t>Auto 41281828</t>
-  </si>
-  <si>
-    <t>AB911816A</t>
+    <t>Auto 86808787</t>
+  </si>
+  <si>
+    <t>AB911846A</t>
   </si>
   <si>
     <t>Test13</t>
   </si>
   <si>
-    <t>10697631</t>
+    <t>10697727</t>
   </si>
   <si>
     <t>457 Recruitment (Vyzeb Vizupe (9457836))</t>
@@ -615,7 +624,7 @@
     <t>NI Retail Assistant</t>
   </si>
   <si>
-    <t>AB911817A</t>
+    <t>AB911847A</t>
   </si>
   <si>
     <t>Female</t>
@@ -639,7 +648,7 @@
     <t>Test14</t>
   </si>
   <si>
-    <t>10697632</t>
+    <t>10697728</t>
   </si>
   <si>
     <t xml:space="preserve">Mr. </t>
@@ -657,7 +666,7 @@
     <t>07 Footwear</t>
   </si>
   <si>
-    <t>AB911818A</t>
+    <t>AB911848A</t>
   </si>
   <si>
     <t>20/06/2004</t>
@@ -672,7 +681,7 @@
     <t>Test15</t>
   </si>
   <si>
-    <t>10697633</t>
+    <t>10697729</t>
   </si>
   <si>
     <t>UkFifteen</t>
@@ -687,7 +696,7 @@
     <t>255 Stockroom</t>
   </si>
   <si>
-    <t>AB911819A</t>
+    <t>AB911849A</t>
   </si>
   <si>
     <t>31/10/2000</t>
@@ -794,7 +803,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
     <fill>
@@ -1284,7 +1293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BO18"/>
+  <dimension ref="A1:BO16"/>
   <sheetFormatPr defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" style="1" customWidth="1"/>
@@ -1727,8 +1736,8 @@
       <c r="A3" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="32" t="s">
-        <v>104</v>
+      <c r="B3" s="32">
+        <v>10697720</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>61</v>
@@ -1918,7 +1927,7 @@
         <v>114</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>105</v>
@@ -1930,7 +1939,7 @@
         <v>64</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H4" s="13" t="s">
         <v>66</v>
@@ -1992,13 +2001,13 @@
         <v>78</v>
       </c>
       <c r="AA4" s="21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AB4" s="7" t="s">
         <v>80</v>
       </c>
       <c r="AC4" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AD4" s="23" t="s">
         <v>82</v>
@@ -2049,7 +2058,7 @@
         <v>92</v>
       </c>
       <c r="AT4" s="29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AU4" s="7" t="s">
         <v>94</v>
@@ -2097,15 +2106,15 @@
         <v>112</v>
       </c>
       <c r="BJ4" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="B5" s="7">
-        <v>10697623</v>
+        <v>120</v>
+      </c>
+      <c r="B5" s="32">
+        <v>10697721</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>61</v>
@@ -2120,7 +2129,7 @@
         <v>64</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>66</v>
@@ -2182,13 +2191,13 @@
         <v>78</v>
       </c>
       <c r="AA5" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="AB5" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="AB5" s="33" t="s">
+      <c r="AC5" s="22" t="s">
         <v>124</v>
-      </c>
-      <c r="AC5" s="22" t="s">
-        <v>125</v>
       </c>
       <c r="AD5" s="23" t="s">
         <v>82</v>
@@ -2231,7 +2240,7 @@
         <v>91</v>
       </c>
       <c r="AQ5" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AR5" s="10" t="s">
         <v>63</v>
@@ -2240,7 +2249,7 @@
         <v>92</v>
       </c>
       <c r="AT5" s="29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AU5" s="7" t="s">
         <v>94</v>
@@ -2288,21 +2297,21 @@
         <v>112</v>
       </c>
       <c r="BJ5" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BN5" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="BO5" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="BO5" s="7" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B6" s="32" t="s">
         <v>130</v>
-      </c>
-      <c r="B6" s="32">
-        <v>10697624</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>61</v>
@@ -2427,7 +2436,7 @@
         <v>91</v>
       </c>
       <c r="AQ6" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AR6" s="10" t="s">
         <v>63</v>
@@ -2575,7 +2584,7 @@
         <v>141</v>
       </c>
       <c r="AB7" s="33" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AC7" s="22" t="s">
         <v>142</v>
@@ -2621,7 +2630,7 @@
         <v>91</v>
       </c>
       <c r="AQ7" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AR7" s="10" t="s">
         <v>63</v>
@@ -2688,8 +2697,8 @@
       <c r="A8" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B8" s="32">
-        <v>10697626</v>
+      <c r="B8" s="32" t="s">
+        <v>147</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>61</v>
@@ -2704,7 +2713,7 @@
         <v>64</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H8" s="13" t="s">
         <v>66</v>
@@ -2766,13 +2775,13 @@
         <v>78</v>
       </c>
       <c r="AA8" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AB8" s="7" t="s">
         <v>80</v>
       </c>
       <c r="AC8" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AD8" s="23" t="s">
         <v>134</v>
@@ -2814,7 +2823,7 @@
         <v>91</v>
       </c>
       <c r="AQ8" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AR8" s="10" t="s">
         <v>63</v>
@@ -2823,7 +2832,7 @@
         <v>92</v>
       </c>
       <c r="AT8" s="29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AU8" s="7" t="s">
         <v>94</v>
@@ -2871,18 +2880,18 @@
         <v>112</v>
       </c>
       <c r="BN8" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BO8" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="B9" s="32">
-        <v>10697627</v>
+        <v>154</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>155</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>61</v>
@@ -2897,7 +2906,7 @@
         <v>64</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>66</v>
@@ -2998,7 +3007,7 @@
         <v>88</v>
       </c>
       <c r="AN9" s="7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AO9" s="7" t="s">
         <v>90</v>
@@ -3016,7 +3025,7 @@
         <v>92</v>
       </c>
       <c r="AT9" s="29" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AU9" s="7" t="s">
         <v>94</v>
@@ -3066,10 +3075,10 @@
     </row>
     <row r="10" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>61</v>
@@ -3084,10 +3093,10 @@
         <v>64</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="I10" s="14" t="s">
         <v>67</v>
@@ -3152,7 +3161,7 @@
         <v>80</v>
       </c>
       <c r="AC10" s="22" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD10" s="23" t="s">
         <v>82</v>
@@ -3185,13 +3194,13 @@
         <v>88</v>
       </c>
       <c r="AN10" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AO10" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AP10" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AQ10" s="10" t="s">
         <v>91</v>
@@ -3203,7 +3212,7 @@
         <v>92</v>
       </c>
       <c r="AT10" s="29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AU10" s="7" t="s">
         <v>94</v>
@@ -3253,10 +3262,10 @@
     </row>
     <row r="11" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="B11" s="32">
-        <v>10697629</v>
+        <v>167</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>168</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>61</v>
@@ -3271,7 +3280,7 @@
         <v>64</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>66</v>
@@ -3339,7 +3348,7 @@
         <v>80</v>
       </c>
       <c r="AC11" s="22" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AD11" s="23" t="s">
         <v>134</v>
@@ -3372,7 +3381,7 @@
         <v>88</v>
       </c>
       <c r="AN11" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AO11" s="7" t="s">
         <v>91</v>
@@ -3390,7 +3399,7 @@
         <v>92</v>
       </c>
       <c r="AT11" s="29" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AU11" s="7" t="s">
         <v>94</v>
@@ -3440,13 +3449,13 @@
     </row>
     <row r="12" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>105</v>
@@ -3458,7 +3467,7 @@
         <v>64</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>66</v>
@@ -3520,13 +3529,13 @@
         <v>78</v>
       </c>
       <c r="AA12" s="21" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AB12" s="33" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AC12" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AD12" s="23" t="s">
         <v>134</v>
@@ -3578,7 +3587,7 @@
         <v>92</v>
       </c>
       <c r="AT12" s="29" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AU12" s="7" t="s">
         <v>94</v>
@@ -3628,10 +3637,10 @@
     </row>
     <row r="13" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="B13" s="32">
-        <v>10697630</v>
+        <v>178</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>179</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>61</v>
@@ -3646,7 +3655,7 @@
         <v>64</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>66</v>
@@ -3708,7 +3717,7 @@
         <v>78</v>
       </c>
       <c r="AA13" s="21" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AB13" s="7" t="s">
         <v>80</v>
@@ -3756,7 +3765,7 @@
         <v>91</v>
       </c>
       <c r="AQ13" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AR13" s="10" t="s">
         <v>63</v>
@@ -3765,7 +3774,7 @@
         <v>92</v>
       </c>
       <c r="AT13" s="29" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AU13" s="7" t="s">
         <v>94</v>
@@ -3821,25 +3830,25 @@
     </row>
     <row r="14" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E14" s="34" t="s">
         <v>63</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H14" s="13" t="s">
         <v>66</v>
@@ -3860,22 +3869,22 @@
         <v>63</v>
       </c>
       <c r="N14" s="16" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="O14" s="16" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="P14" s="14" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="R14" s="17" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="S14" s="14" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="T14" s="36" t="s">
         <v>69</v>
@@ -3928,7 +3937,7 @@
         <v>84</v>
       </c>
       <c r="AJ14" s="39" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AK14" s="43" t="s">
         <v>86</v>
@@ -3940,13 +3949,13 @@
         <v>88</v>
       </c>
       <c r="AN14" s="39" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AO14" s="39" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AP14" s="39" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AQ14" s="10" t="s">
         <v>91</v>
@@ -3958,10 +3967,10 @@
         <v>92</v>
       </c>
       <c r="AT14" s="29" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AU14" s="7" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AV14" s="30">
         <v>38081</v>
@@ -3970,28 +3979,28 @@
         <v>63</v>
       </c>
       <c r="AX14" s="7" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AY14" s="30" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AZ14" s="30" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="BA14" s="30">
         <v>45020</v>
       </c>
       <c r="BB14" s="45" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="BC14" s="46" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="BD14" s="10" t="s">
         <v>63</v>
       </c>
       <c r="BE14" s="10" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="BF14" s="44">
         <v>200052</v>
@@ -4003,30 +4012,30 @@
         <v>101</v>
       </c>
       <c r="BI14" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E15" s="34" t="s">
         <v>63</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H15" s="13" t="s">
         <v>66</v>
@@ -4047,22 +4056,22 @@
         <v>63</v>
       </c>
       <c r="N15" s="16" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="O15" s="16" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="P15" s="14" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="R15" s="17" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="S15" s="14" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="T15" s="36" t="s">
         <v>69</v>
@@ -4091,13 +4100,13 @@
         <v>79</v>
       </c>
       <c r="AB15" s="39" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AC15" s="47" t="s">
         <v>81</v>
       </c>
       <c r="AD15" s="39" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AE15" s="40">
         <v>457</v>
@@ -4128,13 +4137,13 @@
         <v>88</v>
       </c>
       <c r="AN15" s="39" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AO15" s="39" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AP15" s="39" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AQ15" s="10" t="s">
         <v>91</v>
@@ -4146,40 +4155,40 @@
         <v>92</v>
       </c>
       <c r="AT15" s="29" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AU15" s="7" t="s">
         <v>94</v>
       </c>
       <c r="AV15" s="30" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AW15" s="10" t="s">
         <v>63</v>
       </c>
       <c r="AX15" s="7" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AY15" s="30" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AZ15" s="30" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="BA15" s="30" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="BB15" s="45" t="s">
         <v>98</v>
       </c>
       <c r="BC15" s="46" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="BD15" s="10" t="s">
         <v>63</v>
       </c>
       <c r="BE15" s="10" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="BF15" s="44">
         <v>200052</v>
@@ -4191,30 +4200,30 @@
         <v>101</v>
       </c>
       <c r="BI15" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E16" s="34" t="s">
         <v>63</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>66</v>
@@ -4235,22 +4244,22 @@
         <v>63</v>
       </c>
       <c r="N16" s="16" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="O16" s="16" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="P16" s="14" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q16" s="14" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="R16" s="17" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="S16" s="14" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="T16" s="36" t="s">
         <v>69</v>
@@ -4279,13 +4288,13 @@
         <v>79</v>
       </c>
       <c r="AB16" s="39" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AC16" s="47" t="s">
         <v>81</v>
       </c>
       <c r="AD16" s="39" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AE16" s="40">
         <v>457</v>
@@ -4316,13 +4325,13 @@
         <v>88</v>
       </c>
       <c r="AN16" s="39" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AO16" s="39" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AP16" s="39" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AQ16" s="10" t="s">
         <v>91</v>
@@ -4334,22 +4343,22 @@
         <v>92</v>
       </c>
       <c r="AT16" s="29" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AU16" s="7" t="s">
         <v>94</v>
       </c>
       <c r="AV16" s="30" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="AW16" s="10" t="s">
         <v>63</v>
       </c>
       <c r="AX16" s="7" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AY16" s="30" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AZ16" s="30" t="s">
         <v>96</v>
@@ -4358,16 +4367,16 @@
         <v>44197</v>
       </c>
       <c r="BB16" s="45" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="BC16" s="46" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="BD16" s="10" t="s">
         <v>63</v>
       </c>
       <c r="BE16" s="10" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="BF16" s="44">
         <v>200052</v>
@@ -4379,14 +4388,8 @@
         <v>101</v>
       </c>
       <c r="BI16" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="17" spans="46:46" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AT17" s="29"/>
-    </row>
-    <row r="18" spans="46:46" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AT18" s="29"/>
+        <v>203</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/Data/Hires/Workday_NewHire_UKNI_Regression_PK14.xlsx
+++ b/Data/Hires/Workday_NewHire_UKNI_Regression_PK14.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C570752-E392-40F3-91AD-21811B6FBEBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C176BDB7-2C0D-4870-875E-BB3A3AB95423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="226">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -213,7 +213,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10697719</t>
+    <t>10697964</t>
   </si>
   <si>
     <t>Passed</t>
@@ -231,7 +231,7 @@
     <t>UkOne</t>
   </si>
   <si>
-    <t>TwentyFiveAprilSeven</t>
+    <t>TwentyFiveAprilTwentyOne</t>
   </si>
   <si>
     <t>161 923 4772</t>
@@ -312,7 +312,7 @@
     <t>National Insurance (NI) Number</t>
   </si>
   <si>
-    <t>AB911835A</t>
+    <t>AB911865A</t>
   </si>
   <si>
     <t>Male</t>
@@ -345,6 +345,412 @@
     <t>Test2</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'UkTwo TwentyFiveAprilTwentyOne' Employee:{10697965}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('//div[@data-automation-id="tooltipsWrapper"]/button[@data-automation-id="inbox_preview"]').first()[22m
+[2m  -   locator resolved to &lt;button class="wdappchrome-w" data-automation-id="inbox_…&gt;…&lt;/button&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #54[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #55[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #56[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #57[22m
+[2m  -   waiting 500ms[22m
+</t>
+  </si>
+  <si>
     <t>Failed</t>
   </si>
   <si>
@@ -354,7 +760,7 @@
     <t>UkTwo</t>
   </si>
   <si>
-    <t>Auto 85284722</t>
+    <t>Auto 56568486</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -366,7 +772,7 @@
     <t xml:space="preserve">251 Management Retail </t>
   </si>
   <si>
-    <t>AB911836A</t>
+    <t>AB911866A</t>
   </si>
   <si>
     <t>UK Management Group 60</t>
@@ -375,19 +781,19 @@
     <t>Test3</t>
   </si>
   <si>
-    <t>Test failed for 'UkThree TwentyFiveAprilSeven' Employee: Errors and AlertsErrorPage Error- You have not entered an amount within the Compensation Guidelines.     (Employee Compensation Event For Hire Employee) &amp; find failed Screenshot Path:-&gt;H:\WorkdayPlaywright/WorkdayFailedScreenshot/2025-04-08T05-49-09-003Z.png</t>
+    <t>Test failed for 'UkThree TwentyFiveAprilTwentyOne' Employee: Errors and AlertsErrorPage Error- You have not entered an amount within the Compensation Guidelines.     (Employee Compensation Event For Hire Employee) &amp; find failed Screenshot Path:-&gt;H:\WorkdayPlaywright/WorkdayFailedScreenshot/2025-04-21T07-30-16-183Z.png</t>
   </si>
   <si>
     <t>UkThree</t>
   </si>
   <si>
-    <t>Auto 47476690</t>
+    <t>Auto 79087609</t>
   </si>
   <si>
     <t>Assistant Manager</t>
   </si>
   <si>
-    <t>AB911837A</t>
+    <t>AB911867A</t>
   </si>
   <si>
     <t>Passed after removing Grade Profile and Step</t>
@@ -396,10 +802,13 @@
     <t>Test4</t>
   </si>
   <si>
+    <t>10697966</t>
+  </si>
+  <si>
     <t>UkFour</t>
   </si>
   <si>
-    <t>Auto 37859426</t>
+    <t>Auto 73423397</t>
   </si>
   <si>
     <t>Fixed Term (Fixed Term)</t>
@@ -411,7 +820,7 @@
     <t>50000</t>
   </si>
   <si>
-    <t>AB911838A</t>
+    <t>AB911868A</t>
   </si>
   <si>
     <t>UK Department Manager 1</t>
@@ -423,13 +832,13 @@
     <t>Test5</t>
   </si>
   <si>
-    <t>10697763</t>
+    <t>10697967</t>
   </si>
   <si>
     <t>UkFive</t>
   </si>
   <si>
-    <t>Auto 82620489</t>
+    <t>Auto 80768499</t>
   </si>
   <si>
     <t>Team Manager - Retail</t>
@@ -438,7 +847,7 @@
     <t>Part time</t>
   </si>
   <si>
-    <t>AB911839A</t>
+    <t>AB911869A</t>
   </si>
   <si>
     <t>Retail - Team Manager</t>
@@ -450,19 +859,19 @@
     <t>Test6</t>
   </si>
   <si>
-    <t>10697722</t>
+    <t>10697968</t>
   </si>
   <si>
     <t>UkSix</t>
   </si>
   <si>
-    <t>Auto 42362593</t>
+    <t>Auto 69473062</t>
   </si>
   <si>
     <t>Visual Merchandising Manager</t>
   </si>
   <si>
-    <t>AB911840A</t>
+    <t>AB911870A</t>
   </si>
   <si>
     <t>UK Visual Merchandising Manager 1</t>
@@ -474,19 +883,19 @@
     <t>Test7</t>
   </si>
   <si>
-    <t>10697764</t>
+    <t>10697969</t>
   </si>
   <si>
     <t>UkSeven</t>
   </si>
   <si>
-    <t>Auto 69844681</t>
+    <t>Auto 13611941</t>
   </si>
   <si>
     <t>P&amp;C Manager Stores</t>
   </si>
   <si>
-    <t>AB911841A</t>
+    <t>AB911871A</t>
   </si>
   <si>
     <t>UK Assistant Manager</t>
@@ -498,7 +907,7 @@
     <t>Test8</t>
   </si>
   <si>
-    <t>10697723</t>
+    <t>10697970</t>
   </si>
   <si>
     <t>UkEight</t>
@@ -507,13 +916,13 @@
     <t>261 Tills</t>
   </si>
   <si>
-    <t>AB911842A</t>
+    <t>AB911872A</t>
   </si>
   <si>
     <t>Test9</t>
   </si>
   <si>
-    <t>10697724</t>
+    <t>10697971</t>
   </si>
   <si>
     <t>UkNine</t>
@@ -531,13 +940,13 @@
     <t>Initial Step-GB VM Nat -23+</t>
   </si>
   <si>
-    <t>AB911843A</t>
+    <t>AB911873A</t>
   </si>
   <si>
     <t>Test10</t>
   </si>
   <si>
-    <t>10697725</t>
+    <t>10697972</t>
   </si>
   <si>
     <t>UkTen</t>
@@ -549,43 +958,43 @@
     <t>250 Human Resources Retail</t>
   </si>
   <si>
-    <t>AB911844A</t>
+    <t>AB911874A</t>
   </si>
   <si>
     <t>Test11</t>
   </si>
   <si>
-    <t>Test failed for 'UkEleven TwentyFiveAprilSeven' Employee: Errors and AlertsErrorPage Error- You have not entered an amount within the Compensation Guidelines.     (Employee Compensation Event For Hire Employee) &amp; find failed Screenshot Path:-&gt;H:\WorkdayPlaywright/WorkdayFailedScreenshot/2025-04-08T05-15-08-030Z.png</t>
+    <t>Test failed for 'UkEleven TwentyFiveAprilTwentyOne' Employee: Errors and AlertsErrorPage Error- You have not entered an amount within the Compensation Guidelines.     (Employee Compensation Event For Hire Employee) &amp; find failed Screenshot Path:-&gt;H:\WorkdayPlaywright/WorkdayFailedScreenshot/2025-04-21T09-06-07-602Z.png</t>
   </si>
   <si>
     <t>UkEleven</t>
   </si>
   <si>
-    <t>Auto 80749403</t>
-  </si>
-  <si>
-    <t>AB911845A</t>
+    <t>Auto 19785937</t>
+  </si>
+  <si>
+    <t>AB911875A</t>
   </si>
   <si>
     <t>Test12</t>
   </si>
   <si>
-    <t>10697726</t>
+    <t>10697973</t>
   </si>
   <si>
     <t>UkTwelve</t>
   </si>
   <si>
-    <t>Auto 86808787</t>
-  </si>
-  <si>
-    <t>AB911846A</t>
+    <t>Auto 913764</t>
+  </si>
+  <si>
+    <t>AB911876A</t>
   </si>
   <si>
     <t>Test13</t>
   </si>
   <si>
-    <t>10697727</t>
+    <t>10697974</t>
   </si>
   <si>
     <t>457 Recruitment (Vyzeb Vizupe (9457836))</t>
@@ -624,7 +1033,7 @@
     <t>NI Retail Assistant</t>
   </si>
   <si>
-    <t>AB911847A</t>
+    <t>AB911877A</t>
   </si>
   <si>
     <t>Female</t>
@@ -648,7 +1057,7 @@
     <t>Test14</t>
   </si>
   <si>
-    <t>10697728</t>
+    <t>10697975</t>
   </si>
   <si>
     <t xml:space="preserve">Mr. </t>
@@ -666,7 +1075,7 @@
     <t>07 Footwear</t>
   </si>
   <si>
-    <t>AB911848A</t>
+    <t>AB911878A</t>
   </si>
   <si>
     <t>20/06/2004</t>
@@ -681,7 +1090,7 @@
     <t>Test15</t>
   </si>
   <si>
-    <t>10697729</t>
+    <t>10697976</t>
   </si>
   <si>
     <t>UkFifteen</t>
@@ -696,7 +1105,7 @@
     <t>255 Stockroom</t>
   </si>
   <si>
-    <t>AB911849A</t>
+    <t>AB911879A</t>
   </si>
   <si>
     <t>31/10/2000</t>
@@ -803,7 +1212,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -1736,14 +2145,14 @@
       <c r="A3" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B3" s="32">
-        <v>10697720</v>
+      <c r="B3" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>63</v>
@@ -1752,7 +2161,7 @@
         <v>64</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H3" s="13" t="s">
         <v>66</v>
@@ -1814,13 +2223,13 @@
         <v>78</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AB3" s="7" t="s">
         <v>80</v>
       </c>
       <c r="AC3" s="22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD3" s="23" t="s">
         <v>82</v>
@@ -1850,10 +2259,10 @@
         <v>87</v>
       </c>
       <c r="AM3" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN3" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO3" s="7" t="s">
         <v>91</v>
@@ -1871,7 +2280,7 @@
         <v>92</v>
       </c>
       <c r="AT3" s="29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AU3" s="7" t="s">
         <v>94</v>
@@ -1916,21 +2325,21 @@
         <v>101</v>
       </c>
       <c r="BI3" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:67" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>63</v>
@@ -1939,7 +2348,7 @@
         <v>64</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H4" s="13" t="s">
         <v>66</v>
@@ -2001,13 +2410,13 @@
         <v>78</v>
       </c>
       <c r="AA4" s="21" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AB4" s="7" t="s">
         <v>80</v>
       </c>
       <c r="AC4" s="22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AD4" s="23" t="s">
         <v>82</v>
@@ -2037,10 +2446,10 @@
         <v>87</v>
       </c>
       <c r="AM4" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN4" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO4" s="7" t="s">
         <v>91</v>
@@ -2058,7 +2467,7 @@
         <v>92</v>
       </c>
       <c r="AT4" s="29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AU4" s="7" t="s">
         <v>94</v>
@@ -2103,24 +2512,24 @@
         <v>101</v>
       </c>
       <c r="BI4" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BJ4" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B5" s="32">
-        <v>10697721</v>
+        <v>121</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>122</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>63</v>
@@ -2129,7 +2538,7 @@
         <v>64</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>66</v>
@@ -2191,13 +2600,13 @@
         <v>78</v>
       </c>
       <c r="AA5" s="21" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AB5" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AC5" s="22" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AD5" s="23" t="s">
         <v>82</v>
@@ -2228,10 +2637,10 @@
         <v>87</v>
       </c>
       <c r="AM5" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN5" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO5" s="7" t="s">
         <v>91</v>
@@ -2240,7 +2649,7 @@
         <v>91</v>
       </c>
       <c r="AQ5" s="10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AR5" s="10" t="s">
         <v>63</v>
@@ -2249,7 +2658,7 @@
         <v>92</v>
       </c>
       <c r="AT5" s="29" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AU5" s="7" t="s">
         <v>94</v>
@@ -2294,30 +2703,30 @@
         <v>101</v>
       </c>
       <c r="BI5" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BJ5" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BN5" s="32" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BO5" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>63</v>
@@ -2326,7 +2735,7 @@
         <v>64</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>66</v>
@@ -2388,16 +2797,16 @@
         <v>78</v>
       </c>
       <c r="AA6" s="21" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AB6" s="7" t="s">
         <v>80</v>
       </c>
       <c r="AC6" s="22" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AD6" s="23" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AE6" s="24">
         <v>519</v>
@@ -2424,10 +2833,10 @@
         <v>87</v>
       </c>
       <c r="AM6" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN6" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO6" s="7" t="s">
         <v>91</v>
@@ -2436,7 +2845,7 @@
         <v>91</v>
       </c>
       <c r="AQ6" s="10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AR6" s="10" t="s">
         <v>63</v>
@@ -2445,7 +2854,7 @@
         <v>92</v>
       </c>
       <c r="AT6" s="29" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AU6" s="7" t="s">
         <v>94</v>
@@ -2490,27 +2899,27 @@
         <v>101</v>
       </c>
       <c r="BI6" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BN6" s="7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="BO6" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>63</v>
@@ -2519,7 +2928,7 @@
         <v>64</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H7" s="13" t="s">
         <v>66</v>
@@ -2581,13 +2990,13 @@
         <v>78</v>
       </c>
       <c r="AA7" s="21" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AB7" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AC7" s="22" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AD7" s="23" t="s">
         <v>82</v>
@@ -2618,10 +3027,10 @@
         <v>87</v>
       </c>
       <c r="AM7" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN7" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO7" s="7" t="s">
         <v>91</v>
@@ -2630,7 +3039,7 @@
         <v>91</v>
       </c>
       <c r="AQ7" s="10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AR7" s="10" t="s">
         <v>63</v>
@@ -2639,7 +3048,7 @@
         <v>92</v>
       </c>
       <c r="AT7" s="29" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AU7" s="7" t="s">
         <v>94</v>
@@ -2684,27 +3093,27 @@
         <v>101</v>
       </c>
       <c r="BI7" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BN7" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BO7" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>63</v>
@@ -2713,7 +3122,7 @@
         <v>64</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H8" s="13" t="s">
         <v>66</v>
@@ -2775,16 +3184,16 @@
         <v>78</v>
       </c>
       <c r="AA8" s="21" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AB8" s="7" t="s">
         <v>80</v>
       </c>
       <c r="AC8" s="22" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AD8" s="23" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AE8" s="24">
         <v>519</v>
@@ -2811,10 +3220,10 @@
         <v>87</v>
       </c>
       <c r="AM8" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN8" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO8" s="7" t="s">
         <v>91</v>
@@ -2823,7 +3232,7 @@
         <v>91</v>
       </c>
       <c r="AQ8" s="10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AR8" s="10" t="s">
         <v>63</v>
@@ -2832,7 +3241,7 @@
         <v>92</v>
       </c>
       <c r="AT8" s="29" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AU8" s="7" t="s">
         <v>94</v>
@@ -2877,21 +3286,21 @@
         <v>101</v>
       </c>
       <c r="BI8" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BN8" s="7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BO8" s="7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>61</v>
@@ -2906,7 +3315,7 @@
         <v>64</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>66</v>
@@ -2977,7 +3386,7 @@
         <v>81</v>
       </c>
       <c r="AD9" s="23" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AE9" s="24">
         <v>519</v>
@@ -3007,7 +3416,7 @@
         <v>88</v>
       </c>
       <c r="AN9" s="7" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AO9" s="7" t="s">
         <v>90</v>
@@ -3025,7 +3434,7 @@
         <v>92</v>
       </c>
       <c r="AT9" s="29" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AU9" s="7" t="s">
         <v>94</v>
@@ -3075,10 +3484,10 @@
     </row>
     <row r="10" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>61</v>
@@ -3093,7 +3502,7 @@
         <v>64</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>66</v>
@@ -3161,7 +3570,7 @@
         <v>80</v>
       </c>
       <c r="AC10" s="22" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AD10" s="23" t="s">
         <v>82</v>
@@ -3194,13 +3603,13 @@
         <v>88</v>
       </c>
       <c r="AN10" s="7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AO10" s="7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AP10" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AQ10" s="10" t="s">
         <v>91</v>
@@ -3212,7 +3621,7 @@
         <v>92</v>
       </c>
       <c r="AT10" s="29" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AU10" s="7" t="s">
         <v>94</v>
@@ -3262,10 +3671,10 @@
     </row>
     <row r="11" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>61</v>
@@ -3280,7 +3689,7 @@
         <v>64</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>66</v>
@@ -3348,10 +3757,10 @@
         <v>80</v>
       </c>
       <c r="AC11" s="22" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AD11" s="23" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AE11" s="24">
         <v>519</v>
@@ -3381,7 +3790,7 @@
         <v>88</v>
       </c>
       <c r="AN11" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AO11" s="7" t="s">
         <v>91</v>
@@ -3399,7 +3808,7 @@
         <v>92</v>
       </c>
       <c r="AT11" s="29" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AU11" s="7" t="s">
         <v>94</v>
@@ -3449,16 +3858,16 @@
     </row>
     <row r="12" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>63</v>
@@ -3467,7 +3876,7 @@
         <v>64</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>66</v>
@@ -3529,16 +3938,16 @@
         <v>78</v>
       </c>
       <c r="AA12" s="21" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AB12" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AC12" s="22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AD12" s="23" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AE12" s="24">
         <v>519</v>
@@ -3566,10 +3975,10 @@
         <v>87</v>
       </c>
       <c r="AM12" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN12" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO12" s="7" t="s">
         <v>91</v>
@@ -3587,7 +3996,7 @@
         <v>92</v>
       </c>
       <c r="AT12" s="29" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AU12" s="7" t="s">
         <v>94</v>
@@ -3632,21 +4041,21 @@
         <v>101</v>
       </c>
       <c r="BI12" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>63</v>
@@ -3655,7 +4064,7 @@
         <v>64</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>66</v>
@@ -3717,16 +4126,16 @@
         <v>78</v>
       </c>
       <c r="AA13" s="21" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AB13" s="7" t="s">
         <v>80</v>
       </c>
       <c r="AC13" s="22" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AD13" s="23" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AE13" s="24">
         <v>519</v>
@@ -3753,10 +4162,10 @@
         <v>87</v>
       </c>
       <c r="AM13" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN13" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO13" s="7" t="s">
         <v>91</v>
@@ -3765,7 +4174,7 @@
         <v>91</v>
       </c>
       <c r="AQ13" s="10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AR13" s="10" t="s">
         <v>63</v>
@@ -3774,7 +4183,7 @@
         <v>92</v>
       </c>
       <c r="AT13" s="29" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AU13" s="7" t="s">
         <v>94</v>
@@ -3819,36 +4228,36 @@
         <v>101</v>
       </c>
       <c r="BI13" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BN13" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="BO13" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E14" s="34" t="s">
         <v>63</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H14" s="13" t="s">
         <v>66</v>
@@ -3869,22 +4278,22 @@
         <v>63</v>
       </c>
       <c r="N14" s="16" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O14" s="16" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P14" s="14" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="R14" s="17" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="S14" s="14" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="T14" s="36" t="s">
         <v>69</v>
@@ -3919,7 +4328,7 @@
         <v>81</v>
       </c>
       <c r="AD14" s="39" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AE14" s="40">
         <v>457</v>
@@ -3937,7 +4346,7 @@
         <v>84</v>
       </c>
       <c r="AJ14" s="39" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AK14" s="43" t="s">
         <v>86</v>
@@ -3949,13 +4358,13 @@
         <v>88</v>
       </c>
       <c r="AN14" s="39" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AO14" s="39" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AP14" s="39" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AQ14" s="10" t="s">
         <v>91</v>
@@ -3967,10 +4376,10 @@
         <v>92</v>
       </c>
       <c r="AT14" s="29" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AU14" s="7" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AV14" s="30">
         <v>38081</v>
@@ -3979,28 +4388,28 @@
         <v>63</v>
       </c>
       <c r="AX14" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AY14" s="30" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AZ14" s="30" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="BA14" s="30">
         <v>45020</v>
       </c>
       <c r="BB14" s="45" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="BC14" s="46" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="BD14" s="10" t="s">
         <v>63</v>
       </c>
       <c r="BE14" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="BF14" s="44">
         <v>200052</v>
@@ -4012,30 +4421,30 @@
         <v>101</v>
       </c>
       <c r="BI14" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E15" s="34" t="s">
         <v>63</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H15" s="13" t="s">
         <v>66</v>
@@ -4056,22 +4465,22 @@
         <v>63</v>
       </c>
       <c r="N15" s="16" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O15" s="16" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P15" s="14" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="R15" s="17" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="S15" s="14" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="T15" s="36" t="s">
         <v>69</v>
@@ -4100,13 +4509,13 @@
         <v>79</v>
       </c>
       <c r="AB15" s="39" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AC15" s="47" t="s">
         <v>81</v>
       </c>
       <c r="AD15" s="39" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AE15" s="40">
         <v>457</v>
@@ -4137,13 +4546,13 @@
         <v>88</v>
       </c>
       <c r="AN15" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AO15" s="39" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AP15" s="39" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AQ15" s="10" t="s">
         <v>91</v>
@@ -4155,40 +4564,40 @@
         <v>92</v>
       </c>
       <c r="AT15" s="29" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AU15" s="7" t="s">
         <v>94</v>
       </c>
       <c r="AV15" s="30" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AW15" s="10" t="s">
         <v>63</v>
       </c>
       <c r="AX15" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AY15" s="30" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AZ15" s="30" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="BA15" s="30" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="BB15" s="45" t="s">
         <v>98</v>
       </c>
       <c r="BC15" s="46" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="BD15" s="10" t="s">
         <v>63</v>
       </c>
       <c r="BE15" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="BF15" s="44">
         <v>200052</v>
@@ -4200,30 +4609,30 @@
         <v>101</v>
       </c>
       <c r="BI15" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E16" s="34" t="s">
         <v>63</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>66</v>
@@ -4244,22 +4653,22 @@
         <v>63</v>
       </c>
       <c r="N16" s="16" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O16" s="16" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P16" s="14" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q16" s="14" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="R16" s="17" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="S16" s="14" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="T16" s="36" t="s">
         <v>69</v>
@@ -4288,13 +4697,13 @@
         <v>79</v>
       </c>
       <c r="AB16" s="39" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AC16" s="47" t="s">
         <v>81</v>
       </c>
       <c r="AD16" s="39" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AE16" s="40">
         <v>457</v>
@@ -4325,13 +4734,13 @@
         <v>88</v>
       </c>
       <c r="AN16" s="39" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AO16" s="39" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AP16" s="39" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AQ16" s="10" t="s">
         <v>91</v>
@@ -4343,22 +4752,22 @@
         <v>92</v>
       </c>
       <c r="AT16" s="29" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AU16" s="7" t="s">
         <v>94</v>
       </c>
       <c r="AV16" s="30" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AW16" s="10" t="s">
         <v>63</v>
       </c>
       <c r="AX16" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AY16" s="30" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AZ16" s="30" t="s">
         <v>96</v>
@@ -4367,16 +4776,16 @@
         <v>44197</v>
       </c>
       <c r="BB16" s="45" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="BC16" s="46" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="BD16" s="10" t="s">
         <v>63</v>
       </c>
       <c r="BE16" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="BF16" s="44">
         <v>200052</v>
@@ -4388,7 +4797,7 @@
         <v>101</v>
       </c>
       <c r="BI16" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Hires/Workday_NewHire_UKNI_Regression_PK14.xlsx
+++ b/Data/Hires/Workday_NewHire_UKNI_Regression_PK14.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C176BDB7-2C0D-4870-875E-BB3A3AB95423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B676BF72-2AE5-4BD9-B6BA-E35A66A0ED20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -1703,70 +1703,70 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BO16"/>
-  <sheetFormatPr defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.21875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.21875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1796875" style="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="1" customWidth="1"/>
     <col min="4" max="4" width="44" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.21875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="6.21875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="13.21875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="15.44140625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="7.109375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="22.77734375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="30.44140625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.21875" style="1" customWidth="1"/>
-    <col min="18" max="19" width="11.109375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="6.21875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="14.109375" style="1" customWidth="1"/>
-    <col min="22" max="22" width="24.21875" style="1" customWidth="1"/>
-    <col min="23" max="23" width="6.21875" style="1" customWidth="1"/>
-    <col min="24" max="24" width="13.77734375" style="1" customWidth="1"/>
-    <col min="25" max="25" width="17.33203125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="9.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.453125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.36328125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.453125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.453125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.6328125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="6.1796875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.1796875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="15.453125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="7.08984375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="22.81640625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="30.453125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.1796875" style="1" customWidth="1"/>
+    <col min="18" max="19" width="11.08984375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="6.1796875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="14.08984375" style="1" customWidth="1"/>
+    <col min="22" max="22" width="24.1796875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="6.1796875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="13.81640625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="17.36328125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="9.81640625" style="1" customWidth="1"/>
     <col min="27" max="27" width="26" style="1" customWidth="1"/>
-    <col min="28" max="28" width="14.33203125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="14.36328125" style="1" customWidth="1"/>
     <col min="29" max="29" width="15" style="1" customWidth="1"/>
     <col min="30" max="30" width="10" style="1" customWidth="1"/>
-    <col min="31" max="31" width="8.6640625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="12.6640625" style="1" customWidth="1"/>
-    <col min="33" max="34" width="22.44140625" style="1" customWidth="1"/>
-    <col min="35" max="35" width="27.109375" style="1" customWidth="1"/>
+    <col min="31" max="31" width="8.6328125" style="1" customWidth="1"/>
+    <col min="32" max="32" width="12.6328125" style="1" customWidth="1"/>
+    <col min="33" max="34" width="22.453125" style="1" customWidth="1"/>
+    <col min="35" max="35" width="27.08984375" style="1" customWidth="1"/>
     <col min="36" max="36" width="10" style="1" customWidth="1"/>
-    <col min="37" max="37" width="19.6640625" style="1" customWidth="1"/>
-    <col min="38" max="38" width="28.33203125" style="1" customWidth="1"/>
-    <col min="39" max="39" width="21.5546875" style="1" customWidth="1"/>
-    <col min="40" max="40" width="22.6640625" style="1" customWidth="1"/>
-    <col min="41" max="42" width="53.6640625" style="1" customWidth="1"/>
-    <col min="43" max="43" width="9.5546875" style="1" customWidth="1"/>
-    <col min="44" max="44" width="15.44140625" style="1" customWidth="1"/>
-    <col min="45" max="45" width="29.88671875" style="1" customWidth="1"/>
-    <col min="46" max="46" width="12.21875" style="1" customWidth="1"/>
-    <col min="47" max="47" width="7.44140625" style="1" customWidth="1"/>
-    <col min="48" max="48" width="11.77734375" style="1" customWidth="1"/>
-    <col min="49" max="49" width="15.44140625" style="1" customWidth="1"/>
+    <col min="37" max="37" width="19.6328125" style="1" customWidth="1"/>
+    <col min="38" max="38" width="28.36328125" style="1" customWidth="1"/>
+    <col min="39" max="39" width="21.54296875" style="1" customWidth="1"/>
+    <col min="40" max="40" width="22.6328125" style="1" customWidth="1"/>
+    <col min="41" max="42" width="53.6328125" style="1" customWidth="1"/>
+    <col min="43" max="43" width="9.54296875" style="1" customWidth="1"/>
+    <col min="44" max="44" width="15.453125" style="1" customWidth="1"/>
+    <col min="45" max="45" width="29.90625" style="1" customWidth="1"/>
+    <col min="46" max="46" width="12.1796875" style="1" customWidth="1"/>
+    <col min="47" max="47" width="7.453125" style="1" customWidth="1"/>
+    <col min="48" max="48" width="11.81640625" style="1" customWidth="1"/>
+    <col min="49" max="49" width="15.453125" style="1" customWidth="1"/>
     <col min="50" max="50" width="14" style="1" customWidth="1"/>
-    <col min="51" max="51" width="11.33203125" style="1" customWidth="1"/>
+    <col min="51" max="51" width="11.36328125" style="1" customWidth="1"/>
     <col min="52" max="52" width="25" style="1" customWidth="1"/>
     <col min="53" max="53" width="17" style="1" customWidth="1"/>
-    <col min="54" max="54" width="30.109375" style="1" customWidth="1"/>
-    <col min="55" max="55" width="9.6640625" style="1" customWidth="1"/>
+    <col min="54" max="54" width="30.08984375" style="1" customWidth="1"/>
+    <col min="55" max="55" width="9.6328125" style="1" customWidth="1"/>
     <col min="56" max="56" width="18" style="1" customWidth="1"/>
-    <col min="57" max="58" width="13.88671875" style="1" customWidth="1"/>
-    <col min="59" max="59" width="15.33203125" style="1" customWidth="1"/>
-    <col min="60" max="60" width="12.6640625" style="1" customWidth="1"/>
-    <col min="61" max="61" width="26.21875" style="1" customWidth="1"/>
-    <col min="62" max="62" width="8.88671875" style="1" customWidth="1"/>
-    <col min="63" max="16384" width="8.88671875" style="1"/>
+    <col min="57" max="58" width="13.90625" style="1" customWidth="1"/>
+    <col min="59" max="59" width="15.36328125" style="1" customWidth="1"/>
+    <col min="60" max="60" width="12.6328125" style="1" customWidth="1"/>
+    <col min="61" max="61" width="26.1796875" style="1" customWidth="1"/>
+    <col min="62" max="62" width="8.90625" style="1" customWidth="1"/>
+    <col min="63" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:67" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:67" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:67" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>59</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:67" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:67" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>103</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:67" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:67" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>114</v>
       </c>
@@ -2518,7 +2518,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>121</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="6" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>131</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="7" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>140</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="8" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>148</v>
       </c>
@@ -3295,7 +3295,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="9" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>156</v>
       </c>
@@ -3482,7 +3482,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>161</v>
       </c>
@@ -3669,7 +3669,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>169</v>
       </c>
@@ -3856,7 +3856,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>175</v>
       </c>
@@ -4044,7 +4044,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>180</v>
       </c>
@@ -4237,7 +4237,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="14" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>185</v>
       </c>
@@ -4424,7 +4424,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="15" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>206</v>
       </c>
@@ -4612,7 +4612,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="16" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>217</v>
       </c>

--- a/Data/Hires/Workday_NewHire_UKNI_Regression_PK14.xlsx
+++ b/Data/Hires/Workday_NewHire_UKNI_Regression_PK14.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C176BDB7-2C0D-4870-875E-BB3A3AB95423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{904E67D7-AA32-446D-8609-E691D0ABCAFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="227">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -213,7 +213,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10697964</t>
+    <t>10698142</t>
   </si>
   <si>
     <t>Passed</t>
@@ -231,7 +231,7 @@
     <t>UkOne</t>
   </si>
   <si>
-    <t>TwentyFiveAprilTwentyOne</t>
+    <t>TwentyFiveMayFiveC</t>
   </si>
   <si>
     <t>161 923 4772</t>
@@ -312,7 +312,7 @@
     <t>National Insurance (NI) Number</t>
   </si>
   <si>
-    <t>AB911865A</t>
+    <t>AB911910A</t>
   </si>
   <si>
     <t>Male</t>
@@ -345,413 +345,7 @@
     <t>Test2</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'UkTwo TwentyFiveAprilTwentyOne' Employee:{10697965}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('//div[@data-automation-id="tooltipsWrapper"]/button[@data-automation-id="inbox_preview"]').first()[22m
-[2m  -   locator resolved to &lt;button class="wdappchrome-w" data-automation-id="inbox_…&gt;…&lt;/button&gt;[22m
-[2m  - attempting click action[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #1[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #2[22m
-[2m  -   waiting 20ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #3[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #4[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #5[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #6[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #7[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #8[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #9[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #10[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #11[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #12[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #13[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #14[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #15[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #16[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #17[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #18[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #19[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #20[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #21[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #22[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #23[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #24[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #25[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #26[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #27[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #28[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #29[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #30[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #31[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #32[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #33[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #34[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #35[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #36[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #37[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #38[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #39[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #40[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #41[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #42[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #43[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #44[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #45[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #46[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #47[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #48[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #49[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #50[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #51[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #52[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #53[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #54[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #55[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #56[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #57[22m
-[2m  -   waiting 500ms[22m
-</t>
-  </si>
-  <si>
-    <t>Failed</t>
+    <t>10698128</t>
   </si>
   <si>
     <t>519 Store Management (Zerab Sepupu (9575064))</t>
@@ -760,7 +354,10 @@
     <t>UkTwo</t>
   </si>
   <si>
-    <t>Auto 56568486</t>
+    <t>TwentyFiveMayFiveD</t>
+  </si>
+  <si>
+    <t>Auto 55944579</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -772,7 +369,7 @@
     <t xml:space="preserve">251 Management Retail </t>
   </si>
   <si>
-    <t>AB911866A</t>
+    <t>AB911896A</t>
   </si>
   <si>
     <t>UK Management Group 60</t>
@@ -781,19 +378,19 @@
     <t>Test3</t>
   </si>
   <si>
-    <t>Test failed for 'UkThree TwentyFiveAprilTwentyOne' Employee: Errors and AlertsErrorPage Error- You have not entered an amount within the Compensation Guidelines.     (Employee Compensation Event For Hire Employee) &amp; find failed Screenshot Path:-&gt;H:\WorkdayPlaywright/WorkdayFailedScreenshot/2025-04-21T07-30-16-183Z.png</t>
+    <t>10698129</t>
   </si>
   <si>
     <t>UkThree</t>
   </si>
   <si>
-    <t>Auto 79087609</t>
+    <t>Auto 57767889</t>
   </si>
   <si>
     <t>Assistant Manager</t>
   </si>
   <si>
-    <t>AB911867A</t>
+    <t>AB911897A</t>
   </si>
   <si>
     <t>Passed after removing Grade Profile and Step</t>
@@ -802,13 +399,13 @@
     <t>Test4</t>
   </si>
   <si>
-    <t>10697966</t>
+    <t>10698130</t>
   </si>
   <si>
     <t>UkFour</t>
   </si>
   <si>
-    <t>Auto 73423397</t>
+    <t>Auto 1946701</t>
   </si>
   <si>
     <t>Fixed Term (Fixed Term)</t>
@@ -820,7 +417,7 @@
     <t>50000</t>
   </si>
   <si>
-    <t>AB911868A</t>
+    <t>AB911898A</t>
   </si>
   <si>
     <t>UK Department Manager 1</t>
@@ -832,13 +429,16 @@
     <t>Test5</t>
   </si>
   <si>
-    <t>10697967</t>
+    <t>10698131</t>
   </si>
   <si>
     <t>UkFive</t>
   </si>
   <si>
-    <t>Auto 80768499</t>
+    <t>TwentyFiveMayFive</t>
+  </si>
+  <si>
+    <t>Auto 21553501</t>
   </si>
   <si>
     <t>Team Manager - Retail</t>
@@ -847,7 +447,7 @@
     <t>Part time</t>
   </si>
   <si>
-    <t>AB911869A</t>
+    <t>AB911899A</t>
   </si>
   <si>
     <t>Retail - Team Manager</t>
@@ -859,19 +459,19 @@
     <t>Test6</t>
   </si>
   <si>
-    <t>10697968</t>
+    <t>10698132</t>
   </si>
   <si>
     <t>UkSix</t>
   </si>
   <si>
-    <t>Auto 69473062</t>
+    <t>Auto 33918076</t>
   </si>
   <si>
     <t>Visual Merchandising Manager</t>
   </si>
   <si>
-    <t>AB911870A</t>
+    <t>AB911900A</t>
   </si>
   <si>
     <t>UK Visual Merchandising Manager 1</t>
@@ -883,19 +483,19 @@
     <t>Test7</t>
   </si>
   <si>
-    <t>10697969</t>
+    <t>10698133</t>
   </si>
   <si>
     <t>UkSeven</t>
   </si>
   <si>
-    <t>Auto 13611941</t>
+    <t>Auto 58051908</t>
   </si>
   <si>
     <t>P&amp;C Manager Stores</t>
   </si>
   <si>
-    <t>AB911871A</t>
+    <t>AB911901A</t>
   </si>
   <si>
     <t>UK Assistant Manager</t>
@@ -907,7 +507,7 @@
     <t>Test8</t>
   </si>
   <si>
-    <t>10697970</t>
+    <t>10698143</t>
   </si>
   <si>
     <t>UkEight</t>
@@ -916,13 +516,13 @@
     <t>261 Tills</t>
   </si>
   <si>
-    <t>AB911872A</t>
+    <t>AB911911A</t>
   </si>
   <si>
     <t>Test9</t>
   </si>
   <si>
-    <t>10697971</t>
+    <t>10698135</t>
   </si>
   <si>
     <t>UkNine</t>
@@ -940,13 +540,13 @@
     <t>Initial Step-GB VM Nat -23+</t>
   </si>
   <si>
-    <t>AB911873A</t>
+    <t>AB911903A</t>
   </si>
   <si>
     <t>Test10</t>
   </si>
   <si>
-    <t>10697972</t>
+    <t>10698144</t>
   </si>
   <si>
     <t>UkTen</t>
@@ -958,43 +558,43 @@
     <t>250 Human Resources Retail</t>
   </si>
   <si>
-    <t>AB911874A</t>
+    <t>AB911912A</t>
   </si>
   <si>
     <t>Test11</t>
   </si>
   <si>
-    <t>Test failed for 'UkEleven TwentyFiveAprilTwentyOne' Employee: Errors and AlertsErrorPage Error- You have not entered an amount within the Compensation Guidelines.     (Employee Compensation Event For Hire Employee) &amp; find failed Screenshot Path:-&gt;H:\WorkdayPlaywright/WorkdayFailedScreenshot/2025-04-21T09-06-07-602Z.png</t>
+    <t>10698137</t>
   </si>
   <si>
     <t>UkEleven</t>
   </si>
   <si>
-    <t>Auto 19785937</t>
-  </si>
-  <si>
-    <t>AB911875A</t>
+    <t>Auto 88153124</t>
+  </si>
+  <si>
+    <t>AB911905A</t>
   </si>
   <si>
     <t>Test12</t>
   </si>
   <si>
-    <t>10697973</t>
+    <t>10698138</t>
   </si>
   <si>
     <t>UkTwelve</t>
   </si>
   <si>
-    <t>Auto 913764</t>
-  </si>
-  <si>
-    <t>AB911876A</t>
+    <t>Auto 86392126</t>
+  </si>
+  <si>
+    <t>AB911906A</t>
   </si>
   <si>
     <t>Test13</t>
   </si>
   <si>
-    <t>10697974</t>
+    <t>10698139</t>
   </si>
   <si>
     <t>457 Recruitment (Vyzeb Vizupe (9457836))</t>
@@ -1033,7 +633,7 @@
     <t>NI Retail Assistant</t>
   </si>
   <si>
-    <t>AB911877A</t>
+    <t>AB911907A</t>
   </si>
   <si>
     <t>Female</t>
@@ -1057,7 +657,7 @@
     <t>Test14</t>
   </si>
   <si>
-    <t>10697975</t>
+    <t>10698140</t>
   </si>
   <si>
     <t xml:space="preserve">Mr. </t>
@@ -1075,7 +675,7 @@
     <t>07 Footwear</t>
   </si>
   <si>
-    <t>AB911878A</t>
+    <t>AB911908A</t>
   </si>
   <si>
     <t>20/06/2004</t>
@@ -1090,7 +690,7 @@
     <t>Test15</t>
   </si>
   <si>
-    <t>10697976</t>
+    <t>10698141</t>
   </si>
   <si>
     <t>UkFifteen</t>
@@ -1105,7 +705,7 @@
     <t>255 Stockroom</t>
   </si>
   <si>
-    <t>AB911879A</t>
+    <t>AB911909A</t>
   </si>
   <si>
     <t>31/10/2000</t>
@@ -1989,7 +1589,7 @@
         <v>69</v>
       </c>
       <c r="L2" s="15">
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="M2" s="10" t="s">
         <v>63</v>
@@ -2026,11 +1626,11 @@
       </c>
       <c r="X2" s="20">
         <f t="shared" ref="X2:X16" si="0">L2</f>
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="Y2" s="18">
         <f t="shared" ref="Y2:Y16" si="1">X2+90</f>
-        <v>45687</v>
+        <v>45807</v>
       </c>
       <c r="Z2" s="14" t="s">
         <v>78</v>
@@ -2149,10 +1749,10 @@
         <v>104</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>63</v>
@@ -2161,10 +1761,10 @@
         <v>64</v>
       </c>
       <c r="G3" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>107</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>66</v>
       </c>
       <c r="I3" s="14" t="s">
         <v>67</v>
@@ -2176,7 +1776,7 @@
         <v>69</v>
       </c>
       <c r="L3" s="15">
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="M3" s="10" t="s">
         <v>63</v>
@@ -2213,11 +1813,11 @@
       </c>
       <c r="X3" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="Y3" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45807</v>
       </c>
       <c r="Z3" s="14" t="s">
         <v>78</v>
@@ -2336,10 +1936,10 @@
         <v>115</v>
       </c>
       <c r="C4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>63</v>
@@ -2351,7 +1951,7 @@
         <v>116</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="I4" s="14" t="s">
         <v>67</v>
@@ -2363,7 +1963,7 @@
         <v>69</v>
       </c>
       <c r="L4" s="15">
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="M4" s="10" t="s">
         <v>63</v>
@@ -2400,11 +2000,11 @@
       </c>
       <c r="X4" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="Y4" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45807</v>
       </c>
       <c r="Z4" s="14" t="s">
         <v>78</v>
@@ -2529,7 +2129,7 @@
         <v>61</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>63</v>
@@ -2541,7 +2141,7 @@
         <v>123</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="I5" s="14" t="s">
         <v>67</v>
@@ -2553,7 +2153,7 @@
         <v>69</v>
       </c>
       <c r="L5" s="15">
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="M5" s="10" t="s">
         <v>63</v>
@@ -2590,11 +2190,11 @@
       </c>
       <c r="X5" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="Y5" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45807</v>
       </c>
       <c r="Z5" s="14" t="s">
         <v>78</v>
@@ -2631,7 +2231,7 @@
       </c>
       <c r="AK5" s="27">
         <f>L5+365</f>
-        <v>45962</v>
+        <v>46082</v>
       </c>
       <c r="AL5" s="14" t="s">
         <v>87</v>
@@ -2726,7 +2326,7 @@
         <v>61</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>63</v>
@@ -2738,7 +2338,7 @@
         <v>133</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>66</v>
+        <v>134</v>
       </c>
       <c r="I6" s="14" t="s">
         <v>67</v>
@@ -2750,7 +2350,7 @@
         <v>69</v>
       </c>
       <c r="L6" s="15">
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="M6" s="10" t="s">
         <v>63</v>
@@ -2787,26 +2387,26 @@
       </c>
       <c r="X6" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="Y6" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45807</v>
       </c>
       <c r="Z6" s="14" t="s">
         <v>78</v>
       </c>
       <c r="AA6" s="21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AB6" s="7" t="s">
         <v>80</v>
       </c>
       <c r="AC6" s="22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AD6" s="23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AE6" s="24">
         <v>519</v>
@@ -2854,7 +2454,7 @@
         <v>92</v>
       </c>
       <c r="AT6" s="29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AU6" s="7" t="s">
         <v>94</v>
@@ -2902,24 +2502,24 @@
         <v>113</v>
       </c>
       <c r="BN6" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BO6" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>63</v>
@@ -2928,10 +2528,10 @@
         <v>64</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>66</v>
+        <v>134</v>
       </c>
       <c r="I7" s="14" t="s">
         <v>67</v>
@@ -2943,7 +2543,7 @@
         <v>69</v>
       </c>
       <c r="L7" s="15">
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>63</v>
@@ -2980,23 +2580,23 @@
       </c>
       <c r="X7" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="Y7" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45807</v>
       </c>
       <c r="Z7" s="14" t="s">
         <v>78</v>
       </c>
       <c r="AA7" s="21" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AB7" s="33" t="s">
         <v>125</v>
       </c>
       <c r="AC7" s="22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AD7" s="23" t="s">
         <v>82</v>
@@ -3021,7 +2621,7 @@
       </c>
       <c r="AK7" s="27">
         <f>L7+365</f>
-        <v>45962</v>
+        <v>46082</v>
       </c>
       <c r="AL7" s="14" t="s">
         <v>87</v>
@@ -3048,7 +2648,7 @@
         <v>92</v>
       </c>
       <c r="AT7" s="29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AU7" s="7" t="s">
         <v>94</v>
@@ -3096,24 +2696,24 @@
         <v>113</v>
       </c>
       <c r="BN7" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BO7" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>63</v>
@@ -3122,10 +2722,10 @@
         <v>64</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>66</v>
+        <v>134</v>
       </c>
       <c r="I8" s="14" t="s">
         <v>67</v>
@@ -3137,7 +2737,7 @@
         <v>69</v>
       </c>
       <c r="L8" s="15">
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="M8" s="10" t="s">
         <v>63</v>
@@ -3174,26 +2774,26 @@
       </c>
       <c r="X8" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="Y8" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45807</v>
       </c>
       <c r="Z8" s="14" t="s">
         <v>78</v>
       </c>
       <c r="AA8" s="21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AB8" s="7" t="s">
         <v>80</v>
       </c>
       <c r="AC8" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AD8" s="23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AE8" s="24">
         <v>519</v>
@@ -3241,7 +2841,7 @@
         <v>92</v>
       </c>
       <c r="AT8" s="29" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AU8" s="7" t="s">
         <v>94</v>
@@ -3289,18 +2889,18 @@
         <v>113</v>
       </c>
       <c r="BN8" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BO8" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>61</v>
@@ -3315,7 +2915,7 @@
         <v>64</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>66</v>
@@ -3330,7 +2930,7 @@
         <v>69</v>
       </c>
       <c r="L9" s="15">
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="M9" s="10" t="s">
         <v>63</v>
@@ -3367,11 +2967,11 @@
       </c>
       <c r="X9" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="Y9" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45807</v>
       </c>
       <c r="Z9" s="14" t="s">
         <v>78</v>
@@ -3386,7 +2986,7 @@
         <v>81</v>
       </c>
       <c r="AD9" s="23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AE9" s="24">
         <v>519</v>
@@ -3416,7 +3016,7 @@
         <v>88</v>
       </c>
       <c r="AN9" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AO9" s="7" t="s">
         <v>90</v>
@@ -3434,7 +3034,7 @@
         <v>92</v>
       </c>
       <c r="AT9" s="29" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AU9" s="7" t="s">
         <v>94</v>
@@ -3484,10 +3084,10 @@
     </row>
     <row r="10" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>61</v>
@@ -3502,10 +3102,10 @@
         <v>64</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>66</v>
+        <v>134</v>
       </c>
       <c r="I10" s="14" t="s">
         <v>67</v>
@@ -3517,7 +3117,7 @@
         <v>69</v>
       </c>
       <c r="L10" s="15">
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="M10" s="10" t="s">
         <v>63</v>
@@ -3554,11 +3154,11 @@
       </c>
       <c r="X10" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="Y10" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45807</v>
       </c>
       <c r="Z10" s="14" t="s">
         <v>78</v>
@@ -3570,7 +3170,7 @@
         <v>80</v>
       </c>
       <c r="AC10" s="22" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AD10" s="23" t="s">
         <v>82</v>
@@ -3603,13 +3203,13 @@
         <v>88</v>
       </c>
       <c r="AN10" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AO10" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AP10" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AQ10" s="10" t="s">
         <v>91</v>
@@ -3621,7 +3221,7 @@
         <v>92</v>
       </c>
       <c r="AT10" s="29" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AU10" s="7" t="s">
         <v>94</v>
@@ -3671,10 +3271,10 @@
     </row>
     <row r="11" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>61</v>
@@ -3689,7 +3289,7 @@
         <v>64</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>66</v>
@@ -3704,7 +3304,7 @@
         <v>69</v>
       </c>
       <c r="L11" s="15">
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="M11" s="10" t="s">
         <v>63</v>
@@ -3741,11 +3341,11 @@
       </c>
       <c r="X11" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="Y11" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45807</v>
       </c>
       <c r="Z11" s="14" t="s">
         <v>78</v>
@@ -3757,10 +3357,10 @@
         <v>80</v>
       </c>
       <c r="AC11" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AD11" s="23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AE11" s="24">
         <v>519</v>
@@ -3790,7 +3390,7 @@
         <v>88</v>
       </c>
       <c r="AN11" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AO11" s="7" t="s">
         <v>91</v>
@@ -3808,7 +3408,7 @@
         <v>92</v>
       </c>
       <c r="AT11" s="29" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AU11" s="7" t="s">
         <v>94</v>
@@ -3858,16 +3458,16 @@
     </row>
     <row r="12" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C12" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>63</v>
@@ -3876,10 +3476,10 @@
         <v>64</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>66</v>
+        <v>134</v>
       </c>
       <c r="I12" s="14" t="s">
         <v>67</v>
@@ -3891,7 +3491,7 @@
         <v>69</v>
       </c>
       <c r="L12" s="15">
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="M12" s="10" t="s">
         <v>63</v>
@@ -3928,17 +3528,17 @@
       </c>
       <c r="X12" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="Y12" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45807</v>
       </c>
       <c r="Z12" s="14" t="s">
         <v>78</v>
       </c>
       <c r="AA12" s="21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AB12" s="33" t="s">
         <v>125</v>
@@ -3947,7 +3547,7 @@
         <v>118</v>
       </c>
       <c r="AD12" s="23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AE12" s="24">
         <v>519</v>
@@ -3969,7 +3569,7 @@
       </c>
       <c r="AK12" s="27">
         <f>L12+365</f>
-        <v>45962</v>
+        <v>46082</v>
       </c>
       <c r="AL12" s="14" t="s">
         <v>87</v>
@@ -3996,7 +3596,7 @@
         <v>92</v>
       </c>
       <c r="AT12" s="29" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AU12" s="7" t="s">
         <v>94</v>
@@ -4046,16 +3646,16 @@
     </row>
     <row r="13" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>63</v>
@@ -4064,10 +3664,10 @@
         <v>64</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>66</v>
+        <v>134</v>
       </c>
       <c r="I13" s="14" t="s">
         <v>67</v>
@@ -4079,7 +3679,7 @@
         <v>69</v>
       </c>
       <c r="L13" s="15">
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>63</v>
@@ -4116,26 +3716,26 @@
       </c>
       <c r="X13" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="Y13" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45807</v>
       </c>
       <c r="Z13" s="14" t="s">
         <v>78</v>
       </c>
       <c r="AA13" s="21" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AB13" s="7" t="s">
         <v>80</v>
       </c>
       <c r="AC13" s="22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AD13" s="23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AE13" s="24">
         <v>519</v>
@@ -4183,7 +3783,7 @@
         <v>92</v>
       </c>
       <c r="AT13" s="29" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AU13" s="7" t="s">
         <v>94</v>
@@ -4231,36 +3831,36 @@
         <v>113</v>
       </c>
       <c r="BN13" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BO13" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E14" s="34" t="s">
         <v>63</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>66</v>
+        <v>134</v>
       </c>
       <c r="I14" s="36" t="s">
         <v>67</v>
@@ -4272,28 +3872,28 @@
         <v>69</v>
       </c>
       <c r="L14" s="15">
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="M14" s="34" t="s">
         <v>63</v>
       </c>
       <c r="N14" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O14" s="16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P14" s="14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R14" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="S14" s="14" t="s">
         <v>194</v>
-      </c>
-      <c r="S14" s="14" t="s">
-        <v>193</v>
       </c>
       <c r="T14" s="36" t="s">
         <v>69</v>
@@ -4309,11 +3909,11 @@
       </c>
       <c r="X14" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="Y14" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45807</v>
       </c>
       <c r="Z14" s="36" t="s">
         <v>78</v>
@@ -4328,7 +3928,7 @@
         <v>81</v>
       </c>
       <c r="AD14" s="39" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AE14" s="40">
         <v>457</v>
@@ -4346,7 +3946,7 @@
         <v>84</v>
       </c>
       <c r="AJ14" s="39" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AK14" s="43" t="s">
         <v>86</v>
@@ -4358,13 +3958,13 @@
         <v>88</v>
       </c>
       <c r="AN14" s="39" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AO14" s="39" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AP14" s="39" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AQ14" s="10" t="s">
         <v>91</v>
@@ -4376,10 +3976,10 @@
         <v>92</v>
       </c>
       <c r="AT14" s="29" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AU14" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AV14" s="30">
         <v>38081</v>
@@ -4388,28 +3988,28 @@
         <v>63</v>
       </c>
       <c r="AX14" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AY14" s="30" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AZ14" s="30" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="BA14" s="30">
         <v>45020</v>
       </c>
       <c r="BB14" s="45" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="BC14" s="46" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="BD14" s="10" t="s">
         <v>63</v>
       </c>
       <c r="BE14" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="BF14" s="44">
         <v>200052</v>
@@ -4421,33 +4021,33 @@
         <v>101</v>
       </c>
       <c r="BI14" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E15" s="34" t="s">
         <v>63</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>66</v>
+        <v>134</v>
       </c>
       <c r="I15" s="36" t="s">
         <v>67</v>
@@ -4459,28 +4059,28 @@
         <v>69</v>
       </c>
       <c r="L15" s="15">
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="M15" s="34" t="s">
         <v>63</v>
       </c>
       <c r="N15" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O15" s="16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P15" s="14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R15" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="S15" s="14" t="s">
         <v>194</v>
-      </c>
-      <c r="S15" s="14" t="s">
-        <v>193</v>
       </c>
       <c r="T15" s="36" t="s">
         <v>69</v>
@@ -4496,11 +4096,11 @@
       </c>
       <c r="X15" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="Y15" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45807</v>
       </c>
       <c r="Z15" s="36" t="s">
         <v>78</v>
@@ -4509,13 +4109,13 @@
         <v>79</v>
       </c>
       <c r="AB15" s="39" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AC15" s="47" t="s">
         <v>81</v>
       </c>
       <c r="AD15" s="39" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AE15" s="40">
         <v>457</v>
@@ -4537,7 +4137,7 @@
       </c>
       <c r="AK15" s="27">
         <f>L15+365</f>
-        <v>45962</v>
+        <v>46082</v>
       </c>
       <c r="AL15" s="14" t="s">
         <v>87</v>
@@ -4546,13 +4146,13 @@
         <v>88</v>
       </c>
       <c r="AN15" s="39" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO15" s="39" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AP15" s="39" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AQ15" s="10" t="s">
         <v>91</v>
@@ -4564,40 +4164,40 @@
         <v>92</v>
       </c>
       <c r="AT15" s="29" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AU15" s="7" t="s">
         <v>94</v>
       </c>
       <c r="AV15" s="30" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AW15" s="10" t="s">
         <v>63</v>
       </c>
       <c r="AX15" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AY15" s="30" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AZ15" s="30" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="BA15" s="30" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="BB15" s="45" t="s">
         <v>98</v>
       </c>
       <c r="BC15" s="46" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="BD15" s="10" t="s">
         <v>63</v>
       </c>
       <c r="BE15" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="BF15" s="44">
         <v>200052</v>
@@ -4609,33 +4209,33 @@
         <v>101</v>
       </c>
       <c r="BI15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B16" s="32" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E16" s="34" t="s">
         <v>63</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>66</v>
+        <v>134</v>
       </c>
       <c r="I16" s="36" t="s">
         <v>67</v>
@@ -4647,28 +4247,28 @@
         <v>69</v>
       </c>
       <c r="L16" s="15">
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="M16" s="34" t="s">
         <v>63</v>
       </c>
       <c r="N16" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O16" s="16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P16" s="14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q16" s="14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="R16" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="S16" s="14" t="s">
         <v>194</v>
-      </c>
-      <c r="S16" s="14" t="s">
-        <v>193</v>
       </c>
       <c r="T16" s="36" t="s">
         <v>69</v>
@@ -4684,11 +4284,11 @@
       </c>
       <c r="X16" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45717</v>
       </c>
       <c r="Y16" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45807</v>
       </c>
       <c r="Z16" s="36" t="s">
         <v>78</v>
@@ -4697,13 +4297,13 @@
         <v>79</v>
       </c>
       <c r="AB16" s="39" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AC16" s="47" t="s">
         <v>81</v>
       </c>
       <c r="AD16" s="39" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AE16" s="40">
         <v>457</v>
@@ -4725,7 +4325,7 @@
       </c>
       <c r="AK16" s="27">
         <f>L16+365</f>
-        <v>45962</v>
+        <v>46082</v>
       </c>
       <c r="AL16" s="14" t="s">
         <v>87</v>
@@ -4734,13 +4334,13 @@
         <v>88</v>
       </c>
       <c r="AN16" s="39" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AO16" s="39" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AP16" s="39" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AQ16" s="10" t="s">
         <v>91</v>
@@ -4752,22 +4352,22 @@
         <v>92</v>
       </c>
       <c r="AT16" s="29" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AU16" s="7" t="s">
         <v>94</v>
       </c>
       <c r="AV16" s="30" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AW16" s="10" t="s">
         <v>63</v>
       </c>
       <c r="AX16" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AY16" s="30" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AZ16" s="30" t="s">
         <v>96</v>
@@ -4776,16 +4376,16 @@
         <v>44197</v>
       </c>
       <c r="BB16" s="45" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="BC16" s="46" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="BD16" s="10" t="s">
         <v>63</v>
       </c>
       <c r="BE16" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="BF16" s="44">
         <v>200052</v>
@@ -4797,7 +4397,7 @@
         <v>101</v>
       </c>
       <c r="BI16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Hires/Workday_NewHire_UKNI_Regression_PK14.xlsx
+++ b/Data/Hires/Workday_NewHire_UKNI_Regression_PK14.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B676BF72-2AE5-4BD9-B6BA-E35A66A0ED20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE4C7798-44B1-4C6D-8B60-AE3E88D5C903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="225">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -213,7 +213,7 @@
     <t>Test1</t>
   </si>
   <si>
-    <t>10697964</t>
+    <t>10698173</t>
   </si>
   <si>
     <t>Passed</t>
@@ -231,7 +231,7 @@
     <t>UkOne</t>
   </si>
   <si>
-    <t>TwentyFiveAprilTwentyOne</t>
+    <t>TwentyFiveMayTwelve</t>
   </si>
   <si>
     <t>161 923 4772</t>
@@ -312,7 +312,7 @@
     <t>National Insurance (NI) Number</t>
   </si>
   <si>
-    <t>AB911865A</t>
+    <t>AB911935A</t>
   </si>
   <si>
     <t>Male</t>
@@ -345,413 +345,7 @@
     <t>Test2</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'UkTwo TwentyFiveAprilTwentyOne' Employee:{10697965}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('//div[@data-automation-id="tooltipsWrapper"]/button[@data-automation-id="inbox_preview"]').first()[22m
-[2m  -   locator resolved to &lt;button class="wdappchrome-w" data-automation-id="inbox_…&gt;…&lt;/button&gt;[22m
-[2m  - attempting click action[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #1[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #2[22m
-[2m  -   waiting 20ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #3[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #4[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #5[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #6[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #7[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #8[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #9[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #10[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #11[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #12[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #13[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #14[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #15[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #16[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #17[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #18[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #19[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #20[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #21[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #22[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #23[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #24[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #25[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #26[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #27[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #28[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #29[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #30[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #31[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #32[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #33[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #34[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #35[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #36[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #37[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #38[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #39[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #40[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #41[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #42[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #43[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #44[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #45[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #46[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #47[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #48[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #49[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #50[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #51[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #52[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #53[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #54[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #55[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #56[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="none" class="css-1jo90af"&gt;…&lt;/div&gt; from &lt;section aria-live="polite" aria-label="Notifications"&gt;…&lt;/section&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #57[22m
-[2m  -   waiting 500ms[22m
-</t>
-  </si>
-  <si>
-    <t>Failed</t>
+    <t>10698174</t>
   </si>
   <si>
     <t>519 Store Management (Zerab Sepupu (9575064))</t>
@@ -760,7 +354,7 @@
     <t>UkTwo</t>
   </si>
   <si>
-    <t>Auto 56568486</t>
+    <t>Auto 38901878</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -772,7 +366,7 @@
     <t xml:space="preserve">251 Management Retail </t>
   </si>
   <si>
-    <t>AB911866A</t>
+    <t>AB911936A</t>
   </si>
   <si>
     <t>UK Management Group 60</t>
@@ -781,19 +375,19 @@
     <t>Test3</t>
   </si>
   <si>
-    <t>Test failed for 'UkThree TwentyFiveAprilTwentyOne' Employee: Errors and AlertsErrorPage Error- You have not entered an amount within the Compensation Guidelines.     (Employee Compensation Event For Hire Employee) &amp; find failed Screenshot Path:-&gt;H:\WorkdayPlaywright/WorkdayFailedScreenshot/2025-04-21T07-30-16-183Z.png</t>
+    <t>10698175</t>
   </si>
   <si>
     <t>UkThree</t>
   </si>
   <si>
-    <t>Auto 79087609</t>
+    <t>Auto 91287552</t>
   </si>
   <si>
     <t>Assistant Manager</t>
   </si>
   <si>
-    <t>AB911867A</t>
+    <t>AB911937A</t>
   </si>
   <si>
     <t>Passed after removing Grade Profile and Step</t>
@@ -802,13 +396,13 @@
     <t>Test4</t>
   </si>
   <si>
-    <t>10697966</t>
+    <t>10698176</t>
   </si>
   <si>
     <t>UkFour</t>
   </si>
   <si>
-    <t>Auto 73423397</t>
+    <t>Auto 59579171</t>
   </si>
   <si>
     <t>Fixed Term (Fixed Term)</t>
@@ -820,7 +414,7 @@
     <t>50000</t>
   </si>
   <si>
-    <t>AB911868A</t>
+    <t>AB911938A</t>
   </si>
   <si>
     <t>UK Department Manager 1</t>
@@ -832,13 +426,13 @@
     <t>Test5</t>
   </si>
   <si>
-    <t>10697967</t>
+    <t>10698177</t>
   </si>
   <si>
     <t>UkFive</t>
   </si>
   <si>
-    <t>Auto 80768499</t>
+    <t>Auto 44370366</t>
   </si>
   <si>
     <t>Team Manager - Retail</t>
@@ -847,7 +441,7 @@
     <t>Part time</t>
   </si>
   <si>
-    <t>AB911869A</t>
+    <t>AB911939A</t>
   </si>
   <si>
     <t>Retail - Team Manager</t>
@@ -859,19 +453,19 @@
     <t>Test6</t>
   </si>
   <si>
-    <t>10697968</t>
+    <t>10698178</t>
   </si>
   <si>
     <t>UkSix</t>
   </si>
   <si>
-    <t>Auto 69473062</t>
+    <t>Auto 73105638</t>
   </si>
   <si>
     <t>Visual Merchandising Manager</t>
   </si>
   <si>
-    <t>AB911870A</t>
+    <t>AB911940A</t>
   </si>
   <si>
     <t>UK Visual Merchandising Manager 1</t>
@@ -883,19 +477,19 @@
     <t>Test7</t>
   </si>
   <si>
-    <t>10697969</t>
+    <t>10698179</t>
   </si>
   <si>
     <t>UkSeven</t>
   </si>
   <si>
-    <t>Auto 13611941</t>
+    <t>Auto 89082959</t>
   </si>
   <si>
     <t>P&amp;C Manager Stores</t>
   </si>
   <si>
-    <t>AB911871A</t>
+    <t>AB911941A</t>
   </si>
   <si>
     <t>UK Assistant Manager</t>
@@ -907,7 +501,7 @@
     <t>Test8</t>
   </si>
   <si>
-    <t>10697970</t>
+    <t>10698180</t>
   </si>
   <si>
     <t>UkEight</t>
@@ -916,13 +510,13 @@
     <t>261 Tills</t>
   </si>
   <si>
-    <t>AB911872A</t>
+    <t>AB911942A</t>
   </si>
   <si>
     <t>Test9</t>
   </si>
   <si>
-    <t>10697971</t>
+    <t>10698181</t>
   </si>
   <si>
     <t>UkNine</t>
@@ -940,13 +534,13 @@
     <t>Initial Step-GB VM Nat -23+</t>
   </si>
   <si>
-    <t>AB911873A</t>
+    <t>AB911943A</t>
   </si>
   <si>
     <t>Test10</t>
   </si>
   <si>
-    <t>10697972</t>
+    <t>10698182</t>
   </si>
   <si>
     <t>UkTen</t>
@@ -958,43 +552,43 @@
     <t>250 Human Resources Retail</t>
   </si>
   <si>
-    <t>AB911874A</t>
+    <t>AB911944A</t>
   </si>
   <si>
     <t>Test11</t>
   </si>
   <si>
-    <t>Test failed for 'UkEleven TwentyFiveAprilTwentyOne' Employee: Errors and AlertsErrorPage Error- You have not entered an amount within the Compensation Guidelines.     (Employee Compensation Event For Hire Employee) &amp; find failed Screenshot Path:-&gt;H:\WorkdayPlaywright/WorkdayFailedScreenshot/2025-04-21T09-06-07-602Z.png</t>
+    <t>10698183</t>
   </si>
   <si>
     <t>UkEleven</t>
   </si>
   <si>
-    <t>Auto 19785937</t>
-  </si>
-  <si>
-    <t>AB911875A</t>
+    <t>Auto 1383274</t>
+  </si>
+  <si>
+    <t>AB911945A</t>
   </si>
   <si>
     <t>Test12</t>
   </si>
   <si>
-    <t>10697973</t>
+    <t>10698184</t>
   </si>
   <si>
     <t>UkTwelve</t>
   </si>
   <si>
-    <t>Auto 913764</t>
-  </si>
-  <si>
-    <t>AB911876A</t>
+    <t>Auto 4982149</t>
+  </si>
+  <si>
+    <t>AB911946A</t>
   </si>
   <si>
     <t>Test13</t>
   </si>
   <si>
-    <t>10697974</t>
+    <t>10698185</t>
   </si>
   <si>
     <t>457 Recruitment (Vyzeb Vizupe (9457836))</t>
@@ -1033,7 +627,7 @@
     <t>NI Retail Assistant</t>
   </si>
   <si>
-    <t>AB911877A</t>
+    <t>AB911947A</t>
   </si>
   <si>
     <t>Female</t>
@@ -1057,7 +651,7 @@
     <t>Test14</t>
   </si>
   <si>
-    <t>10697975</t>
+    <t>10698186</t>
   </si>
   <si>
     <t xml:space="preserve">Mr. </t>
@@ -1075,7 +669,7 @@
     <t>07 Footwear</t>
   </si>
   <si>
-    <t>AB911878A</t>
+    <t>AB911948A</t>
   </si>
   <si>
     <t>20/06/2004</t>
@@ -1090,7 +684,7 @@
     <t>Test15</t>
   </si>
   <si>
-    <t>10697976</t>
+    <t>10698187</t>
   </si>
   <si>
     <t>UkFifteen</t>
@@ -1105,7 +699,7 @@
     <t>255 Stockroom</t>
   </si>
   <si>
-    <t>AB911879A</t>
+    <t>AB911949A</t>
   </si>
   <si>
     <t>31/10/2000</t>
@@ -1703,70 +1297,70 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BO16"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1796875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.21875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.21875" style="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="1" customWidth="1"/>
     <col min="4" max="4" width="44" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.453125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="6.36328125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.453125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6328125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="6.1796875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="13.1796875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="15.453125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="7.08984375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="22.81640625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="30.453125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.1796875" style="1" customWidth="1"/>
-    <col min="18" max="19" width="11.08984375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="6.1796875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="14.08984375" style="1" customWidth="1"/>
-    <col min="22" max="22" width="24.1796875" style="1" customWidth="1"/>
-    <col min="23" max="23" width="6.1796875" style="1" customWidth="1"/>
-    <col min="24" max="24" width="13.81640625" style="1" customWidth="1"/>
-    <col min="25" max="25" width="17.36328125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="9.81640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="6.21875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.21875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="15.44140625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="7.109375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="22.77734375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="30.44140625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.21875" style="1" customWidth="1"/>
+    <col min="18" max="19" width="11.109375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="6.21875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="14.109375" style="1" customWidth="1"/>
+    <col min="22" max="22" width="24.21875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="6.21875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="13.77734375" style="1" customWidth="1"/>
+    <col min="25" max="25" width="17.33203125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="9.77734375" style="1" customWidth="1"/>
     <col min="27" max="27" width="26" style="1" customWidth="1"/>
-    <col min="28" max="28" width="14.36328125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="14.33203125" style="1" customWidth="1"/>
     <col min="29" max="29" width="15" style="1" customWidth="1"/>
     <col min="30" max="30" width="10" style="1" customWidth="1"/>
-    <col min="31" max="31" width="8.6328125" style="1" customWidth="1"/>
-    <col min="32" max="32" width="12.6328125" style="1" customWidth="1"/>
-    <col min="33" max="34" width="22.453125" style="1" customWidth="1"/>
-    <col min="35" max="35" width="27.08984375" style="1" customWidth="1"/>
+    <col min="31" max="31" width="8.6640625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="12.6640625" style="1" customWidth="1"/>
+    <col min="33" max="34" width="22.44140625" style="1" customWidth="1"/>
+    <col min="35" max="35" width="27.109375" style="1" customWidth="1"/>
     <col min="36" max="36" width="10" style="1" customWidth="1"/>
-    <col min="37" max="37" width="19.6328125" style="1" customWidth="1"/>
-    <col min="38" max="38" width="28.36328125" style="1" customWidth="1"/>
-    <col min="39" max="39" width="21.54296875" style="1" customWidth="1"/>
-    <col min="40" max="40" width="22.6328125" style="1" customWidth="1"/>
-    <col min="41" max="42" width="53.6328125" style="1" customWidth="1"/>
-    <col min="43" max="43" width="9.54296875" style="1" customWidth="1"/>
-    <col min="44" max="44" width="15.453125" style="1" customWidth="1"/>
-    <col min="45" max="45" width="29.90625" style="1" customWidth="1"/>
-    <col min="46" max="46" width="12.1796875" style="1" customWidth="1"/>
-    <col min="47" max="47" width="7.453125" style="1" customWidth="1"/>
-    <col min="48" max="48" width="11.81640625" style="1" customWidth="1"/>
-    <col min="49" max="49" width="15.453125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="19.6640625" style="1" customWidth="1"/>
+    <col min="38" max="38" width="28.33203125" style="1" customWidth="1"/>
+    <col min="39" max="39" width="21.5546875" style="1" customWidth="1"/>
+    <col min="40" max="40" width="22.6640625" style="1" customWidth="1"/>
+    <col min="41" max="42" width="53.6640625" style="1" customWidth="1"/>
+    <col min="43" max="43" width="9.5546875" style="1" customWidth="1"/>
+    <col min="44" max="44" width="15.44140625" style="1" customWidth="1"/>
+    <col min="45" max="45" width="29.88671875" style="1" customWidth="1"/>
+    <col min="46" max="46" width="12.21875" style="1" customWidth="1"/>
+    <col min="47" max="47" width="7.44140625" style="1" customWidth="1"/>
+    <col min="48" max="48" width="11.77734375" style="1" customWidth="1"/>
+    <col min="49" max="49" width="15.44140625" style="1" customWidth="1"/>
     <col min="50" max="50" width="14" style="1" customWidth="1"/>
-    <col min="51" max="51" width="11.36328125" style="1" customWidth="1"/>
+    <col min="51" max="51" width="11.33203125" style="1" customWidth="1"/>
     <col min="52" max="52" width="25" style="1" customWidth="1"/>
     <col min="53" max="53" width="17" style="1" customWidth="1"/>
-    <col min="54" max="54" width="30.08984375" style="1" customWidth="1"/>
-    <col min="55" max="55" width="9.6328125" style="1" customWidth="1"/>
+    <col min="54" max="54" width="30.109375" style="1" customWidth="1"/>
+    <col min="55" max="55" width="9.6640625" style="1" customWidth="1"/>
     <col min="56" max="56" width="18" style="1" customWidth="1"/>
-    <col min="57" max="58" width="13.90625" style="1" customWidth="1"/>
-    <col min="59" max="59" width="15.36328125" style="1" customWidth="1"/>
-    <col min="60" max="60" width="12.6328125" style="1" customWidth="1"/>
-    <col min="61" max="61" width="26.1796875" style="1" customWidth="1"/>
-    <col min="62" max="62" width="8.90625" style="1" customWidth="1"/>
-    <col min="63" max="16384" width="8.90625" style="1"/>
+    <col min="57" max="58" width="13.88671875" style="1" customWidth="1"/>
+    <col min="59" max="59" width="15.33203125" style="1" customWidth="1"/>
+    <col min="60" max="60" width="12.6640625" style="1" customWidth="1"/>
+    <col min="61" max="61" width="26.21875" style="1" customWidth="1"/>
+    <col min="62" max="62" width="8.88671875" style="1" customWidth="1"/>
+    <col min="63" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:67" s="2" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1954,7 +1548,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:67" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:67" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>59</v>
       </c>
@@ -1989,7 +1583,7 @@
         <v>69</v>
       </c>
       <c r="L2" s="15">
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="M2" s="10" t="s">
         <v>63</v>
@@ -2026,11 +1620,11 @@
       </c>
       <c r="X2" s="20">
         <f t="shared" ref="X2:X16" si="0">L2</f>
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="Y2" s="18">
         <f t="shared" ref="Y2:Y16" si="1">X2+90</f>
-        <v>45687</v>
+        <v>45838</v>
       </c>
       <c r="Z2" s="14" t="s">
         <v>78</v>
@@ -2141,7 +1735,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:67" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:67" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>103</v>
       </c>
@@ -2149,10 +1743,10 @@
         <v>104</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>63</v>
@@ -2161,7 +1755,7 @@
         <v>64</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H3" s="13" t="s">
         <v>66</v>
@@ -2176,7 +1770,7 @@
         <v>69</v>
       </c>
       <c r="L3" s="15">
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="M3" s="10" t="s">
         <v>63</v>
@@ -2213,23 +1807,23 @@
       </c>
       <c r="X3" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="Y3" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45838</v>
       </c>
       <c r="Z3" s="14" t="s">
         <v>78</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AB3" s="7" t="s">
         <v>80</v>
       </c>
       <c r="AC3" s="22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AD3" s="23" t="s">
         <v>82</v>
@@ -2259,10 +1853,10 @@
         <v>87</v>
       </c>
       <c r="AM3" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="AN3" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="AN3" s="7" t="s">
-        <v>111</v>
       </c>
       <c r="AO3" s="7" t="s">
         <v>91</v>
@@ -2280,7 +1874,7 @@
         <v>92</v>
       </c>
       <c r="AT3" s="29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AU3" s="7" t="s">
         <v>94</v>
@@ -2325,21 +1919,21 @@
         <v>101</v>
       </c>
       <c r="BI3" s="14" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:67" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="4" spans="1:67" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="B4" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="B4" s="32" t="s">
-        <v>115</v>
-      </c>
       <c r="C4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>63</v>
@@ -2348,7 +1942,7 @@
         <v>64</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H4" s="13" t="s">
         <v>66</v>
@@ -2363,7 +1957,7 @@
         <v>69</v>
       </c>
       <c r="L4" s="15">
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="M4" s="10" t="s">
         <v>63</v>
@@ -2400,23 +1994,23 @@
       </c>
       <c r="X4" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="Y4" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45838</v>
       </c>
       <c r="Z4" s="14" t="s">
         <v>78</v>
       </c>
       <c r="AA4" s="21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AB4" s="7" t="s">
         <v>80</v>
       </c>
       <c r="AC4" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AD4" s="23" t="s">
         <v>82</v>
@@ -2446,10 +2040,10 @@
         <v>87</v>
       </c>
       <c r="AM4" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="AN4" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="AN4" s="7" t="s">
-        <v>111</v>
       </c>
       <c r="AO4" s="7" t="s">
         <v>91</v>
@@ -2467,7 +2061,7 @@
         <v>92</v>
       </c>
       <c r="AT4" s="29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AU4" s="7" t="s">
         <v>94</v>
@@ -2512,24 +2106,24 @@
         <v>101</v>
       </c>
       <c r="BI4" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="BJ4" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="5" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+      <c r="B5" s="32" t="s">
         <v>121</v>
-      </c>
-      <c r="B5" s="32" t="s">
-        <v>122</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>63</v>
@@ -2538,7 +2132,7 @@
         <v>64</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>66</v>
@@ -2553,7 +2147,7 @@
         <v>69</v>
       </c>
       <c r="L5" s="15">
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="M5" s="10" t="s">
         <v>63</v>
@@ -2590,23 +2184,23 @@
       </c>
       <c r="X5" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="Y5" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45838</v>
       </c>
       <c r="Z5" s="14" t="s">
         <v>78</v>
       </c>
       <c r="AA5" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB5" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="AB5" s="33" t="s">
+      <c r="AC5" s="22" t="s">
         <v>125</v>
-      </c>
-      <c r="AC5" s="22" t="s">
-        <v>126</v>
       </c>
       <c r="AD5" s="23" t="s">
         <v>82</v>
@@ -2631,16 +2225,16 @@
       </c>
       <c r="AK5" s="27">
         <f>L5+365</f>
-        <v>45962</v>
+        <v>46113</v>
       </c>
       <c r="AL5" s="14" t="s">
         <v>87</v>
       </c>
       <c r="AM5" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="AN5" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="AN5" s="7" t="s">
-        <v>111</v>
       </c>
       <c r="AO5" s="7" t="s">
         <v>91</v>
@@ -2649,7 +2243,7 @@
         <v>91</v>
       </c>
       <c r="AQ5" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AR5" s="10" t="s">
         <v>63</v>
@@ -2658,7 +2252,7 @@
         <v>92</v>
       </c>
       <c r="AT5" s="29" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AU5" s="7" t="s">
         <v>94</v>
@@ -2703,30 +2297,30 @@
         <v>101</v>
       </c>
       <c r="BI5" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="BJ5" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BN5" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="BO5" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="BO5" s="7" t="s">
+    </row>
+    <row r="6" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="6" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+      <c r="B6" s="32" t="s">
         <v>131</v>
-      </c>
-      <c r="B6" s="32" t="s">
-        <v>132</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>63</v>
@@ -2735,7 +2329,7 @@
         <v>64</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>66</v>
@@ -2750,7 +2344,7 @@
         <v>69</v>
       </c>
       <c r="L6" s="15">
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="M6" s="10" t="s">
         <v>63</v>
@@ -2787,26 +2381,26 @@
       </c>
       <c r="X6" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="Y6" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45838</v>
       </c>
       <c r="Z6" s="14" t="s">
         <v>78</v>
       </c>
       <c r="AA6" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AB6" s="7" t="s">
         <v>80</v>
       </c>
       <c r="AC6" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="AD6" s="23" t="s">
         <v>135</v>
-      </c>
-      <c r="AD6" s="23" t="s">
-        <v>136</v>
       </c>
       <c r="AE6" s="24">
         <v>519</v>
@@ -2833,10 +2427,10 @@
         <v>87</v>
       </c>
       <c r="AM6" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="AN6" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="AN6" s="7" t="s">
-        <v>111</v>
       </c>
       <c r="AO6" s="7" t="s">
         <v>91</v>
@@ -2845,7 +2439,7 @@
         <v>91</v>
       </c>
       <c r="AQ6" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AR6" s="10" t="s">
         <v>63</v>
@@ -2854,7 +2448,7 @@
         <v>92</v>
       </c>
       <c r="AT6" s="29" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AU6" s="7" t="s">
         <v>94</v>
@@ -2899,27 +2493,27 @@
         <v>101</v>
       </c>
       <c r="BI6" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="BN6" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="BO6" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="BO6" s="7" t="s">
+    </row>
+    <row r="7" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="7" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
+      <c r="B7" s="32" t="s">
         <v>140</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>141</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>63</v>
@@ -2928,7 +2522,7 @@
         <v>64</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H7" s="13" t="s">
         <v>66</v>
@@ -2943,7 +2537,7 @@
         <v>69</v>
       </c>
       <c r="L7" s="15">
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>63</v>
@@ -2980,23 +2574,23 @@
       </c>
       <c r="X7" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="Y7" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45838</v>
       </c>
       <c r="Z7" s="14" t="s">
         <v>78</v>
       </c>
       <c r="AA7" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="AB7" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC7" s="22" t="s">
         <v>143</v>
-      </c>
-      <c r="AB7" s="33" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC7" s="22" t="s">
-        <v>144</v>
       </c>
       <c r="AD7" s="23" t="s">
         <v>82</v>
@@ -3021,16 +2615,16 @@
       </c>
       <c r="AK7" s="27">
         <f>L7+365</f>
-        <v>45962</v>
+        <v>46113</v>
       </c>
       <c r="AL7" s="14" t="s">
         <v>87</v>
       </c>
       <c r="AM7" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="AN7" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="AN7" s="7" t="s">
-        <v>111</v>
       </c>
       <c r="AO7" s="7" t="s">
         <v>91</v>
@@ -3039,7 +2633,7 @@
         <v>91</v>
       </c>
       <c r="AQ7" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AR7" s="10" t="s">
         <v>63</v>
@@ -3048,7 +2642,7 @@
         <v>92</v>
       </c>
       <c r="AT7" s="29" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AU7" s="7" t="s">
         <v>94</v>
@@ -3093,27 +2687,27 @@
         <v>101</v>
       </c>
       <c r="BI7" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="BN7" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="BO7" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="BO7" s="7" t="s">
+    </row>
+    <row r="8" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="8" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
+      <c r="B8" s="32" t="s">
         <v>148</v>
-      </c>
-      <c r="B8" s="32" t="s">
-        <v>149</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>63</v>
@@ -3122,7 +2716,7 @@
         <v>64</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H8" s="13" t="s">
         <v>66</v>
@@ -3137,7 +2731,7 @@
         <v>69</v>
       </c>
       <c r="L8" s="15">
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="M8" s="10" t="s">
         <v>63</v>
@@ -3174,26 +2768,26 @@
       </c>
       <c r="X8" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="Y8" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45838</v>
       </c>
       <c r="Z8" s="14" t="s">
         <v>78</v>
       </c>
       <c r="AA8" s="21" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AB8" s="7" t="s">
         <v>80</v>
       </c>
       <c r="AC8" s="22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AD8" s="23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AE8" s="24">
         <v>519</v>
@@ -3220,10 +2814,10 @@
         <v>87</v>
       </c>
       <c r="AM8" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="AN8" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="AN8" s="7" t="s">
-        <v>111</v>
       </c>
       <c r="AO8" s="7" t="s">
         <v>91</v>
@@ -3232,7 +2826,7 @@
         <v>91</v>
       </c>
       <c r="AQ8" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AR8" s="10" t="s">
         <v>63</v>
@@ -3241,7 +2835,7 @@
         <v>92</v>
       </c>
       <c r="AT8" s="29" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AU8" s="7" t="s">
         <v>94</v>
@@ -3286,21 +2880,21 @@
         <v>101</v>
       </c>
       <c r="BI8" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="BN8" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="BO8" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="BO8" s="7" t="s">
+    </row>
+    <row r="9" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="9" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
+      <c r="B9" s="32" t="s">
         <v>156</v>
-      </c>
-      <c r="B9" s="32" t="s">
-        <v>157</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>61</v>
@@ -3315,7 +2909,7 @@
         <v>64</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>66</v>
@@ -3330,7 +2924,7 @@
         <v>69</v>
       </c>
       <c r="L9" s="15">
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="M9" s="10" t="s">
         <v>63</v>
@@ -3367,11 +2961,11 @@
       </c>
       <c r="X9" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="Y9" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45838</v>
       </c>
       <c r="Z9" s="14" t="s">
         <v>78</v>
@@ -3386,7 +2980,7 @@
         <v>81</v>
       </c>
       <c r="AD9" s="23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AE9" s="24">
         <v>519</v>
@@ -3416,7 +3010,7 @@
         <v>88</v>
       </c>
       <c r="AN9" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AO9" s="7" t="s">
         <v>90</v>
@@ -3434,7 +3028,7 @@
         <v>92</v>
       </c>
       <c r="AT9" s="29" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AU9" s="7" t="s">
         <v>94</v>
@@ -3482,12 +3076,12 @@
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B10" s="32" t="s">
         <v>161</v>
-      </c>
-      <c r="B10" s="32" t="s">
-        <v>162</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>61</v>
@@ -3502,7 +3096,7 @@
         <v>64</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>66</v>
@@ -3517,7 +3111,7 @@
         <v>69</v>
       </c>
       <c r="L10" s="15">
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="M10" s="10" t="s">
         <v>63</v>
@@ -3554,11 +3148,11 @@
       </c>
       <c r="X10" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="Y10" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45838</v>
       </c>
       <c r="Z10" s="14" t="s">
         <v>78</v>
@@ -3570,7 +3164,7 @@
         <v>80</v>
       </c>
       <c r="AC10" s="22" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AD10" s="23" t="s">
         <v>82</v>
@@ -3603,13 +3197,13 @@
         <v>88</v>
       </c>
       <c r="AN10" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="AO10" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="AO10" s="7" t="s">
+      <c r="AP10" s="7" t="s">
         <v>166</v>
-      </c>
-      <c r="AP10" s="7" t="s">
-        <v>167</v>
       </c>
       <c r="AQ10" s="10" t="s">
         <v>91</v>
@@ -3621,7 +3215,7 @@
         <v>92</v>
       </c>
       <c r="AT10" s="29" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AU10" s="7" t="s">
         <v>94</v>
@@ -3669,12 +3263,12 @@
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B11" s="32" t="s">
         <v>169</v>
-      </c>
-      <c r="B11" s="32" t="s">
-        <v>170</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>61</v>
@@ -3689,7 +3283,7 @@
         <v>64</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>66</v>
@@ -3704,7 +3298,7 @@
         <v>69</v>
       </c>
       <c r="L11" s="15">
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="M11" s="10" t="s">
         <v>63</v>
@@ -3741,11 +3335,11 @@
       </c>
       <c r="X11" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="Y11" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45838</v>
       </c>
       <c r="Z11" s="14" t="s">
         <v>78</v>
@@ -3757,10 +3351,10 @@
         <v>80</v>
       </c>
       <c r="AC11" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AD11" s="23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AE11" s="24">
         <v>519</v>
@@ -3790,7 +3384,7 @@
         <v>88</v>
       </c>
       <c r="AN11" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AO11" s="7" t="s">
         <v>91</v>
@@ -3808,7 +3402,7 @@
         <v>92</v>
       </c>
       <c r="AT11" s="29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AU11" s="7" t="s">
         <v>94</v>
@@ -3856,18 +3450,18 @@
         <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="B12" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="B12" s="32" t="s">
-        <v>176</v>
-      </c>
       <c r="C12" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>63</v>
@@ -3876,7 +3470,7 @@
         <v>64</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>66</v>
@@ -3891,7 +3485,7 @@
         <v>69</v>
       </c>
       <c r="L12" s="15">
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="M12" s="10" t="s">
         <v>63</v>
@@ -3928,26 +3522,26 @@
       </c>
       <c r="X12" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="Y12" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45838</v>
       </c>
       <c r="Z12" s="14" t="s">
         <v>78</v>
       </c>
       <c r="AA12" s="21" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB12" s="33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AC12" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AD12" s="23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AE12" s="24">
         <v>519</v>
@@ -3969,16 +3563,16 @@
       </c>
       <c r="AK12" s="27">
         <f>L12+365</f>
-        <v>45962</v>
+        <v>46113</v>
       </c>
       <c r="AL12" s="14" t="s">
         <v>87</v>
       </c>
       <c r="AM12" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="AN12" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="AN12" s="7" t="s">
-        <v>111</v>
       </c>
       <c r="AO12" s="7" t="s">
         <v>91</v>
@@ -3996,7 +3590,7 @@
         <v>92</v>
       </c>
       <c r="AT12" s="29" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AU12" s="7" t="s">
         <v>94</v>
@@ -4041,21 +3635,21 @@
         <v>101</v>
       </c>
       <c r="BI12" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
-    <row r="13" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="B13" s="32" t="s">
         <v>180</v>
-      </c>
-      <c r="B13" s="32" t="s">
-        <v>181</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>63</v>
@@ -4064,7 +3658,7 @@
         <v>64</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>66</v>
@@ -4079,7 +3673,7 @@
         <v>69</v>
       </c>
       <c r="L13" s="15">
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>63</v>
@@ -4116,26 +3710,26 @@
       </c>
       <c r="X13" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="Y13" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45838</v>
       </c>
       <c r="Z13" s="14" t="s">
         <v>78</v>
       </c>
       <c r="AA13" s="21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AB13" s="7" t="s">
         <v>80</v>
       </c>
       <c r="AC13" s="22" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AD13" s="23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AE13" s="24">
         <v>519</v>
@@ -4162,10 +3756,10 @@
         <v>87</v>
       </c>
       <c r="AM13" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="AN13" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="AN13" s="7" t="s">
-        <v>111</v>
       </c>
       <c r="AO13" s="7" t="s">
         <v>91</v>
@@ -4174,7 +3768,7 @@
         <v>91</v>
       </c>
       <c r="AQ13" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AR13" s="10" t="s">
         <v>63</v>
@@ -4183,7 +3777,7 @@
         <v>92</v>
       </c>
       <c r="AT13" s="29" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AU13" s="7" t="s">
         <v>94</v>
@@ -4228,36 +3822,36 @@
         <v>101</v>
       </c>
       <c r="BI13" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="BN13" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="BO13" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="BO13" s="7" t="s">
-        <v>147</v>
-      </c>
     </row>
-    <row r="14" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B14" s="32" t="s">
         <v>185</v>
-      </c>
-      <c r="B14" s="32" t="s">
-        <v>186</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D14" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="35" t="s">
         <v>187</v>
       </c>
-      <c r="E14" s="34" t="s">
-        <v>63</v>
-      </c>
-      <c r="F14" s="35" t="s">
+      <c r="G14" s="12" t="s">
         <v>188</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>189</v>
       </c>
       <c r="H14" s="13" t="s">
         <v>66</v>
@@ -4272,28 +3866,28 @@
         <v>69</v>
       </c>
       <c r="L14" s="15">
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="M14" s="34" t="s">
         <v>63</v>
       </c>
       <c r="N14" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="O14" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="O14" s="16" t="s">
+      <c r="P14" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="P14" s="14" t="s">
+      <c r="Q14" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="Q14" s="14" t="s">
+      <c r="R14" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="R14" s="17" t="s">
-        <v>194</v>
-      </c>
       <c r="S14" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="T14" s="36" t="s">
         <v>69</v>
@@ -4309,11 +3903,11 @@
       </c>
       <c r="X14" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="Y14" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45838</v>
       </c>
       <c r="Z14" s="36" t="s">
         <v>78</v>
@@ -4328,7 +3922,7 @@
         <v>81</v>
       </c>
       <c r="AD14" s="39" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AE14" s="40">
         <v>457</v>
@@ -4346,7 +3940,7 @@
         <v>84</v>
       </c>
       <c r="AJ14" s="39" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AK14" s="43" t="s">
         <v>86</v>
@@ -4358,13 +3952,13 @@
         <v>88</v>
       </c>
       <c r="AN14" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="AO14" s="39" t="s">
         <v>196</v>
       </c>
-      <c r="AO14" s="39" t="s">
+      <c r="AP14" s="39" t="s">
         <v>197</v>
-      </c>
-      <c r="AP14" s="39" t="s">
-        <v>198</v>
       </c>
       <c r="AQ14" s="10" t="s">
         <v>91</v>
@@ -4376,10 +3970,10 @@
         <v>92</v>
       </c>
       <c r="AT14" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="AU14" s="7" t="s">
         <v>199</v>
-      </c>
-      <c r="AU14" s="7" t="s">
-        <v>200</v>
       </c>
       <c r="AV14" s="30">
         <v>38081</v>
@@ -4388,28 +3982,28 @@
         <v>63</v>
       </c>
       <c r="AX14" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AY14" s="30" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AZ14" s="30" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="BA14" s="30">
         <v>45020</v>
       </c>
       <c r="BB14" s="45" t="s">
+        <v>201</v>
+      </c>
+      <c r="BC14" s="46" t="s">
         <v>202</v>
       </c>
-      <c r="BC14" s="46" t="s">
+      <c r="BD14" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="BE14" s="10" t="s">
         <v>203</v>
-      </c>
-      <c r="BD14" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="BE14" s="10" t="s">
-        <v>204</v>
       </c>
       <c r="BF14" s="44">
         <v>200052</v>
@@ -4421,30 +4015,30 @@
         <v>101</v>
       </c>
       <c r="BI14" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="15" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="15" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
+      <c r="B15" s="32" t="s">
         <v>206</v>
-      </c>
-      <c r="B15" s="32" t="s">
-        <v>207</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E15" s="34" t="s">
         <v>63</v>
       </c>
       <c r="F15" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="G15" s="12" t="s">
         <v>208</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>209</v>
       </c>
       <c r="H15" s="13" t="s">
         <v>66</v>
@@ -4459,28 +4053,28 @@
         <v>69</v>
       </c>
       <c r="L15" s="15">
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="M15" s="34" t="s">
         <v>63</v>
       </c>
       <c r="N15" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="O15" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="O15" s="16" t="s">
+      <c r="P15" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="P15" s="14" t="s">
+      <c r="Q15" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="Q15" s="14" t="s">
+      <c r="R15" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="R15" s="17" t="s">
-        <v>194</v>
-      </c>
       <c r="S15" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="T15" s="36" t="s">
         <v>69</v>
@@ -4496,11 +4090,11 @@
       </c>
       <c r="X15" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="Y15" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45838</v>
       </c>
       <c r="Z15" s="36" t="s">
         <v>78</v>
@@ -4509,13 +4103,13 @@
         <v>79</v>
       </c>
       <c r="AB15" s="39" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AC15" s="47" t="s">
         <v>81</v>
       </c>
       <c r="AD15" s="39" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AE15" s="40">
         <v>457</v>
@@ -4537,7 +4131,7 @@
       </c>
       <c r="AK15" s="27">
         <f>L15+365</f>
-        <v>45962</v>
+        <v>46113</v>
       </c>
       <c r="AL15" s="14" t="s">
         <v>87</v>
@@ -4546,13 +4140,13 @@
         <v>88</v>
       </c>
       <c r="AN15" s="39" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AO15" s="39" t="s">
+        <v>196</v>
+      </c>
+      <c r="AP15" s="39" t="s">
         <v>197</v>
-      </c>
-      <c r="AP15" s="39" t="s">
-        <v>198</v>
       </c>
       <c r="AQ15" s="10" t="s">
         <v>91</v>
@@ -4564,40 +4158,40 @@
         <v>92</v>
       </c>
       <c r="AT15" s="29" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AU15" s="7" t="s">
         <v>94</v>
       </c>
       <c r="AV15" s="30" t="s">
+        <v>213</v>
+      </c>
+      <c r="AW15" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="AX15" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="AY15" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="AZ15" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="AW15" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AX15" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="AY15" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="AZ15" s="30" t="s">
+      <c r="BA15" s="30" t="s">
         <v>215</v>
-      </c>
-      <c r="BA15" s="30" t="s">
-        <v>216</v>
       </c>
       <c r="BB15" s="45" t="s">
         <v>98</v>
       </c>
       <c r="BC15" s="46" t="s">
+        <v>202</v>
+      </c>
+      <c r="BD15" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="BE15" s="10" t="s">
         <v>203</v>
-      </c>
-      <c r="BD15" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="BE15" s="10" t="s">
-        <v>204</v>
       </c>
       <c r="BF15" s="44">
         <v>200052</v>
@@ -4609,30 +4203,30 @@
         <v>101</v>
       </c>
       <c r="BI15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
-    <row r="16" spans="1:67" s="7" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:67" s="7" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B16" s="32" t="s">
         <v>217</v>
-      </c>
-      <c r="B16" s="32" t="s">
-        <v>218</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E16" s="34" t="s">
         <v>63</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>66</v>
@@ -4647,28 +4241,28 @@
         <v>69</v>
       </c>
       <c r="L16" s="15">
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="M16" s="34" t="s">
         <v>63</v>
       </c>
       <c r="N16" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="O16" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="O16" s="16" t="s">
+      <c r="P16" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="P16" s="14" t="s">
+      <c r="Q16" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="Q16" s="14" t="s">
+      <c r="R16" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="R16" s="17" t="s">
-        <v>194</v>
-      </c>
       <c r="S16" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="T16" s="36" t="s">
         <v>69</v>
@@ -4684,11 +4278,11 @@
       </c>
       <c r="X16" s="20">
         <f t="shared" si="0"/>
-        <v>45597</v>
+        <v>45748</v>
       </c>
       <c r="Y16" s="18">
         <f t="shared" si="1"/>
-        <v>45687</v>
+        <v>45838</v>
       </c>
       <c r="Z16" s="36" t="s">
         <v>78</v>
@@ -4697,13 +4291,13 @@
         <v>79</v>
       </c>
       <c r="AB16" s="39" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AC16" s="47" t="s">
         <v>81</v>
       </c>
       <c r="AD16" s="39" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AE16" s="40">
         <v>457</v>
@@ -4725,7 +4319,7 @@
       </c>
       <c r="AK16" s="27">
         <f>L16+365</f>
-        <v>45962</v>
+        <v>46113</v>
       </c>
       <c r="AL16" s="14" t="s">
         <v>87</v>
@@ -4734,13 +4328,13 @@
         <v>88</v>
       </c>
       <c r="AN16" s="39" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AO16" s="39" t="s">
+        <v>196</v>
+      </c>
+      <c r="AP16" s="39" t="s">
         <v>197</v>
-      </c>
-      <c r="AP16" s="39" t="s">
-        <v>198</v>
       </c>
       <c r="AQ16" s="10" t="s">
         <v>91</v>
@@ -4752,22 +4346,22 @@
         <v>92</v>
       </c>
       <c r="AT16" s="29" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AU16" s="7" t="s">
         <v>94</v>
       </c>
       <c r="AV16" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AW16" s="10" t="s">
         <v>63</v>
       </c>
       <c r="AX16" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AY16" s="30" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AZ16" s="30" t="s">
         <v>96</v>
@@ -4776,16 +4370,16 @@
         <v>44197</v>
       </c>
       <c r="BB16" s="45" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="BC16" s="46" t="s">
+        <v>202</v>
+      </c>
+      <c r="BD16" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="BE16" s="10" t="s">
         <v>203</v>
-      </c>
-      <c r="BD16" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="BE16" s="10" t="s">
-        <v>204</v>
       </c>
       <c r="BF16" s="44">
         <v>200052</v>
@@ -4797,7 +4391,7 @@
         <v>101</v>
       </c>
       <c r="BI16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
